--- a/Bibsam_tidskriftslistor/bibsam_data_oxford.xlsx
+++ b/Bibsam_tidskriftslistor/bibsam_data_oxford.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F8AD3E-828F-4A34-A627-C08B88D1629E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E904C30-344D-4F75-8420-5F4A70FBDB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="1659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3256" uniqueCount="1662">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -4997,6 +4997,15 @@
   </si>
   <si>
     <t>https://academic.oup.com/jpr</t>
+  </si>
+  <si>
+    <t>1535-4989</t>
+  </si>
+  <si>
+    <t>American Journal of Respiratory Cell and Molecular Biology</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/ajrcmb</t>
   </si>
 </sst>
 </file>
@@ -5063,8 +5072,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}" name="Table2" displayName="Table2" ref="A1:G532" totalsRowShown="0">
-  <autoFilter ref="A1:G532" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}" name="Table2" displayName="Table2" ref="A1:G533" totalsRowShown="0">
+  <autoFilter ref="A1:G533" xr:uid="{29F4AE4F-3C6D-4BE0-8AAF-431A9A218867}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G533">
+    <sortCondition ref="D1:D533"/>
+  </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F5E2486E-E90D-461C-972F-7C4D25D666D5}" name="Imprint"/>
     <tableColumn id="2" xr3:uid="{4D955E89-3276-4531-A1BC-F7793CABE6EA}" name="ISSN Electronic"/>
@@ -5341,7 +5353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34547141-E29C-4D3C-A0EC-D02E1559D016}">
-  <dimension ref="A1:G532"/>
+  <dimension ref="A1:G533"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -5718,13 +5730,13 @@
         <v>872</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>1659</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>1660</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>1661</v>
       </c>
       <c r="F19" t="s">
         <v>871</v>
@@ -5738,13 +5750,13 @@
         <v>872</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>871</v>
@@ -5758,16 +5770,13 @@
         <v>872</v>
       </c>
       <c r="B21" t="s">
-        <v>926</v>
-      </c>
-      <c r="C21" t="s">
-        <v>938</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>939</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>1185</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
         <v>871</v>
@@ -5781,16 +5790,19 @@
         <v>872</v>
       </c>
       <c r="B22" t="s">
-        <v>948</v>
+        <v>926</v>
+      </c>
+      <c r="C22" t="s">
+        <v>938</v>
       </c>
       <c r="D22" t="s">
-        <v>949</v>
+        <v>939</v>
       </c>
       <c r="E22" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F22" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G22" t="s">
         <v>873</v>
@@ -5801,16 +5813,16 @@
         <v>872</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>948</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>949</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>1186</v>
       </c>
       <c r="F23" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G23" t="s">
         <v>873</v>
@@ -5821,13 +5833,13 @@
         <v>872</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
         <v>871</v>
@@ -5841,13 +5853,13 @@
         <v>872</v>
       </c>
       <c r="B25" t="s">
-        <v>1597</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>1598</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
-        <v>1599</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s">
         <v>871</v>
@@ -5861,13 +5873,13 @@
         <v>872</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>1597</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>1598</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>1599</v>
       </c>
       <c r="F26" t="s">
         <v>871</v>
@@ -5881,16 +5893,13 @@
         <v>872</v>
       </c>
       <c r="B27" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1473</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>1474</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>1475</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
         <v>871</v>
@@ -5904,13 +5913,16 @@
         <v>872</v>
       </c>
       <c r="B28" t="s">
-        <v>1187</v>
+        <v>1472</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1473</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>1474</v>
       </c>
       <c r="E28" t="s">
-        <v>1188</v>
+        <v>1475</v>
       </c>
       <c r="F28" t="s">
         <v>871</v>
@@ -5924,16 +5936,16 @@
         <v>872</v>
       </c>
       <c r="B29" t="s">
-        <v>950</v>
+        <v>1187</v>
       </c>
       <c r="D29" t="s">
-        <v>951</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F29" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G29" t="s">
         <v>873</v>
@@ -5944,13 +5956,13 @@
         <v>872</v>
       </c>
       <c r="B30" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D30" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E30" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F30" t="s">
         <v>947</v>
@@ -5964,16 +5976,16 @@
         <v>872</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>952</v>
       </c>
       <c r="D31" t="s">
-        <v>60</v>
+        <v>953</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>1190</v>
       </c>
       <c r="F31" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G31" t="s">
         <v>873</v>
@@ -5984,16 +5996,13 @@
         <v>872</v>
       </c>
       <c r="B32" t="s">
-        <v>851</v>
-      </c>
-      <c r="C32" t="s">
-        <v>852</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>853</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>854</v>
+        <v>61</v>
       </c>
       <c r="F32" t="s">
         <v>871</v>
@@ -6007,13 +6016,16 @@
         <v>872</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>851</v>
+      </c>
+      <c r="C33" t="s">
+        <v>852</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>853</v>
       </c>
       <c r="E33" t="s">
-        <v>64</v>
+        <v>854</v>
       </c>
       <c r="F33" t="s">
         <v>871</v>
@@ -6027,13 +6039,13 @@
         <v>872</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
         <v>871</v>
@@ -6067,13 +6079,13 @@
         <v>872</v>
       </c>
       <c r="B36" t="s">
-        <v>1409</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>1410</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>1411</v>
+        <v>67</v>
       </c>
       <c r="F36" t="s">
         <v>871</v>
@@ -6087,16 +6099,16 @@
         <v>872</v>
       </c>
       <c r="B37" t="s">
-        <v>954</v>
+        <v>1409</v>
       </c>
       <c r="D37" t="s">
-        <v>955</v>
+        <v>1410</v>
       </c>
       <c r="E37" t="s">
-        <v>1191</v>
+        <v>1411</v>
       </c>
       <c r="F37" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G37" t="s">
         <v>873</v>
@@ -6107,13 +6119,13 @@
         <v>872</v>
       </c>
       <c r="B38" t="s">
-        <v>1600</v>
+        <v>954</v>
       </c>
       <c r="D38" t="s">
-        <v>1601</v>
+        <v>955</v>
       </c>
       <c r="E38" t="s">
-        <v>1602</v>
+        <v>1191</v>
       </c>
       <c r="F38" t="s">
         <v>947</v>
@@ -6127,16 +6139,16 @@
         <v>872</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>1600</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>1601</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>1602</v>
       </c>
       <c r="F39" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G39" t="s">
         <v>873</v>
@@ -6147,16 +6159,16 @@
         <v>872</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G40" t="s">
         <v>873</v>
@@ -6167,13 +6179,13 @@
         <v>872</v>
       </c>
       <c r="B41" t="s">
-        <v>1138</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>1125</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>1139</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
         <v>947</v>
@@ -6187,16 +6199,16 @@
         <v>872</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>1138</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>1125</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>1139</v>
       </c>
       <c r="F42" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G42" t="s">
         <v>873</v>
@@ -6207,16 +6219,16 @@
         <v>872</v>
       </c>
       <c r="B43" t="s">
-        <v>956</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>1192</v>
+        <v>77</v>
       </c>
       <c r="E43" t="s">
-        <v>1193</v>
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G43" t="s">
         <v>873</v>
@@ -6227,16 +6239,16 @@
         <v>872</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>956</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>1192</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>1193</v>
       </c>
       <c r="F44" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G44" t="s">
         <v>873</v>
@@ -6247,13 +6259,13 @@
         <v>872</v>
       </c>
       <c r="B45" t="s">
-        <v>1412</v>
+        <v>79</v>
       </c>
       <c r="D45" t="s">
-        <v>1413</v>
+        <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>1414</v>
+        <v>81</v>
       </c>
       <c r="F45" t="s">
         <v>871</v>
@@ -6267,13 +6279,13 @@
         <v>872</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>1412</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>1413</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>1414</v>
       </c>
       <c r="F46" t="s">
         <v>871</v>
@@ -6287,13 +6299,13 @@
         <v>872</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>1194</v>
+        <v>84</v>
       </c>
       <c r="F47" t="s">
         <v>871</v>
@@ -6307,16 +6319,13 @@
         <v>872</v>
       </c>
       <c r="B48" t="s">
-        <v>874</v>
-      </c>
-      <c r="C48" t="s">
-        <v>875</v>
+        <v>85</v>
       </c>
       <c r="D48" t="s">
-        <v>1195</v>
+        <v>86</v>
       </c>
       <c r="E48" t="s">
-        <v>876</v>
+        <v>1194</v>
       </c>
       <c r="F48" t="s">
         <v>871</v>
@@ -6330,13 +6339,16 @@
         <v>872</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>874</v>
+      </c>
+      <c r="C49" t="s">
+        <v>875</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>1195</v>
       </c>
       <c r="E49" t="s">
-        <v>1196</v>
+        <v>876</v>
       </c>
       <c r="F49" t="s">
         <v>871</v>
@@ -6350,16 +6362,16 @@
         <v>872</v>
       </c>
       <c r="B50" t="s">
-        <v>1415</v>
+        <v>87</v>
       </c>
       <c r="D50" t="s">
-        <v>1416</v>
+        <v>88</v>
       </c>
       <c r="E50" t="s">
-        <v>1417</v>
+        <v>1196</v>
       </c>
       <c r="F50" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G50" t="s">
         <v>873</v>
@@ -6370,13 +6382,13 @@
         <v>872</v>
       </c>
       <c r="B51" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D51" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="E51" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="F51" t="s">
         <v>947</v>
@@ -6390,13 +6402,13 @@
         <v>872</v>
       </c>
       <c r="B52" t="s">
-        <v>1471</v>
+        <v>1418</v>
       </c>
       <c r="D52" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="E52" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="F52" t="s">
         <v>947</v>
@@ -6410,13 +6422,13 @@
         <v>872</v>
       </c>
       <c r="B53" t="s">
-        <v>957</v>
+        <v>1471</v>
       </c>
       <c r="D53" t="s">
-        <v>958</v>
+        <v>1421</v>
       </c>
       <c r="E53" t="s">
-        <v>1197</v>
+        <v>1422</v>
       </c>
       <c r="F53" t="s">
         <v>947</v>
@@ -6430,16 +6442,16 @@
         <v>872</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>957</v>
       </c>
       <c r="D54" t="s">
-        <v>90</v>
+        <v>958</v>
       </c>
       <c r="E54" t="s">
-        <v>91</v>
+        <v>1197</v>
       </c>
       <c r="F54" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G54" t="s">
         <v>873</v>
@@ -6450,13 +6462,16 @@
         <v>872</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>915</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1603</v>
       </c>
       <c r="D55" t="s">
-        <v>93</v>
+        <v>1604</v>
       </c>
       <c r="E55" t="s">
-        <v>94</v>
+        <v>914</v>
       </c>
       <c r="F55" t="s">
         <v>871</v>
@@ -6470,16 +6485,16 @@
         <v>872</v>
       </c>
       <c r="B56" t="s">
-        <v>959</v>
+        <v>89</v>
       </c>
       <c r="D56" t="s">
-        <v>960</v>
+        <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>1198</v>
+        <v>91</v>
       </c>
       <c r="F56" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G56" t="s">
         <v>873</v>
@@ -6490,16 +6505,16 @@
         <v>872</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D57" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E57" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F57" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G57" t="s">
         <v>873</v>
@@ -6510,13 +6525,13 @@
         <v>872</v>
       </c>
       <c r="B58" t="s">
-        <v>98</v>
+        <v>959</v>
       </c>
       <c r="D58" t="s">
-        <v>99</v>
+        <v>960</v>
       </c>
       <c r="E58" t="s">
-        <v>100</v>
+        <v>1198</v>
       </c>
       <c r="F58" t="s">
         <v>947</v>
@@ -6530,16 +6545,16 @@
         <v>872</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E59" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F59" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G59" t="s">
         <v>873</v>
@@ -6550,16 +6565,16 @@
         <v>872</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E60" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F60" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G60" t="s">
         <v>873</v>
@@ -6570,13 +6585,13 @@
         <v>872</v>
       </c>
       <c r="B61" t="s">
-        <v>1199</v>
+        <v>101</v>
       </c>
       <c r="D61" t="s">
-        <v>1200</v>
+        <v>102</v>
       </c>
       <c r="E61" t="s">
-        <v>1201</v>
+        <v>103</v>
       </c>
       <c r="F61" t="s">
         <v>871</v>
@@ -6590,13 +6605,13 @@
         <v>872</v>
       </c>
       <c r="B62" t="s">
-        <v>1423</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>1424</v>
+        <v>105</v>
       </c>
       <c r="E62" t="s">
-        <v>1425</v>
+        <v>106</v>
       </c>
       <c r="F62" t="s">
         <v>871</v>
@@ -6610,16 +6625,13 @@
         <v>872</v>
       </c>
       <c r="B63" t="s">
-        <v>915</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1603</v>
+        <v>1199</v>
       </c>
       <c r="D63" t="s">
-        <v>1604</v>
+        <v>1200</v>
       </c>
       <c r="E63" t="s">
-        <v>914</v>
+        <v>1201</v>
       </c>
       <c r="F63" t="s">
         <v>871</v>
@@ -6633,13 +6645,13 @@
         <v>872</v>
       </c>
       <c r="B64" t="s">
-        <v>109</v>
+        <v>1423</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>1424</v>
       </c>
       <c r="E64" t="s">
-        <v>111</v>
+        <v>1425</v>
       </c>
       <c r="F64" t="s">
         <v>871</v>
@@ -6653,13 +6665,13 @@
         <v>872</v>
       </c>
       <c r="B65" t="s">
-        <v>1426</v>
+        <v>109</v>
       </c>
       <c r="D65" t="s">
-        <v>1427</v>
+        <v>110</v>
       </c>
       <c r="E65" t="s">
-        <v>1428</v>
+        <v>111</v>
       </c>
       <c r="F65" t="s">
         <v>871</v>
@@ -6673,13 +6685,13 @@
         <v>872</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>1426</v>
       </c>
       <c r="D66" t="s">
-        <v>115</v>
+        <v>1427</v>
       </c>
       <c r="E66" t="s">
-        <v>116</v>
+        <v>1428</v>
       </c>
       <c r="F66" t="s">
         <v>871</v>
@@ -6693,16 +6705,16 @@
         <v>872</v>
       </c>
       <c r="B67" t="s">
-        <v>961</v>
+        <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>1202</v>
+        <v>115</v>
       </c>
       <c r="E67" t="s">
-        <v>1203</v>
+        <v>116</v>
       </c>
       <c r="F67" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G67" t="s">
         <v>873</v>
@@ -6713,16 +6725,16 @@
         <v>872</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>961</v>
       </c>
       <c r="D68" t="s">
-        <v>118</v>
+        <v>1202</v>
       </c>
       <c r="E68" t="s">
-        <v>119</v>
+        <v>1203</v>
       </c>
       <c r="F68" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G68" t="s">
         <v>873</v>
@@ -6733,13 +6745,13 @@
         <v>872</v>
       </c>
       <c r="B69" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E69" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F69" t="s">
         <v>871</v>
@@ -6753,13 +6765,13 @@
         <v>872</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D70" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
         <v>871</v>
@@ -6773,13 +6785,13 @@
         <v>872</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E71" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F71" t="s">
         <v>871</v>
@@ -6793,13 +6805,13 @@
         <v>872</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E72" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F72" t="s">
         <v>871</v>
@@ -6813,13 +6825,13 @@
         <v>872</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E73" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F73" t="s">
         <v>871</v>
@@ -6833,13 +6845,13 @@
         <v>872</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E74" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F74" t="s">
         <v>871</v>
@@ -6853,13 +6865,13 @@
         <v>872</v>
       </c>
       <c r="B75" t="s">
-        <v>1429</v>
+        <v>137</v>
       </c>
       <c r="D75" t="s">
-        <v>1430</v>
+        <v>138</v>
       </c>
       <c r="E75" t="s">
-        <v>1431</v>
+        <v>139</v>
       </c>
       <c r="F75" t="s">
         <v>871</v>
@@ -6873,13 +6885,13 @@
         <v>872</v>
       </c>
       <c r="B76" t="s">
-        <v>1605</v>
+        <v>1429</v>
       </c>
       <c r="D76" t="s">
-        <v>1606</v>
+        <v>1430</v>
       </c>
       <c r="E76" t="s">
-        <v>1607</v>
+        <v>1431</v>
       </c>
       <c r="F76" t="s">
         <v>871</v>
@@ -6893,13 +6905,13 @@
         <v>872</v>
       </c>
       <c r="B77" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="D77" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="E77" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="F77" t="s">
         <v>871</v>
@@ -6913,13 +6925,13 @@
         <v>872</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>1608</v>
       </c>
       <c r="D78" t="s">
-        <v>143</v>
+        <v>1609</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>1610</v>
       </c>
       <c r="F78" t="s">
         <v>871</v>
@@ -6933,13 +6945,13 @@
         <v>872</v>
       </c>
       <c r="B79" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E79" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F79" t="s">
         <v>871</v>
@@ -6953,13 +6965,13 @@
         <v>872</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D80" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E80" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F80" t="s">
         <v>871</v>
@@ -6973,19 +6985,16 @@
         <v>872</v>
       </c>
       <c r="B81" t="s">
-        <v>962</v>
-      </c>
-      <c r="C81" t="s">
-        <v>963</v>
+        <v>150</v>
       </c>
       <c r="D81" t="s">
-        <v>964</v>
+        <v>151</v>
       </c>
       <c r="E81" t="s">
-        <v>1204</v>
+        <v>152</v>
       </c>
       <c r="F81" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G81" t="s">
         <v>873</v>
@@ -6996,16 +7005,19 @@
         <v>872</v>
       </c>
       <c r="B82" t="s">
-        <v>936</v>
+        <v>962</v>
+      </c>
+      <c r="C82" t="s">
+        <v>963</v>
       </c>
       <c r="D82" t="s">
-        <v>1476</v>
+        <v>964</v>
       </c>
       <c r="E82" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G82" t="s">
         <v>873</v>
@@ -7016,13 +7028,13 @@
         <v>872</v>
       </c>
       <c r="B83" t="s">
-        <v>1205</v>
+        <v>936</v>
       </c>
       <c r="D83" t="s">
-        <v>1206</v>
+        <v>1476</v>
       </c>
       <c r="E83" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F83" t="s">
         <v>871</v>
@@ -7036,13 +7048,13 @@
         <v>872</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>1205</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>1206</v>
       </c>
       <c r="E84" t="s">
-        <v>155</v>
+        <v>1207</v>
       </c>
       <c r="F84" t="s">
         <v>871</v>
@@ -7056,13 +7068,13 @@
         <v>872</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E85" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F85" t="s">
         <v>871</v>
@@ -7076,19 +7088,16 @@
         <v>872</v>
       </c>
       <c r="B86" t="s">
-        <v>965</v>
-      </c>
-      <c r="C86" t="s">
-        <v>966</v>
+        <v>156</v>
       </c>
       <c r="D86" t="s">
-        <v>967</v>
+        <v>157</v>
       </c>
       <c r="E86" t="s">
-        <v>1209</v>
+        <v>158</v>
       </c>
       <c r="F86" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G86" t="s">
         <v>873</v>
@@ -7099,16 +7108,19 @@
         <v>872</v>
       </c>
       <c r="B87" t="s">
-        <v>159</v>
+        <v>965</v>
+      </c>
+      <c r="C87" t="s">
+        <v>966</v>
       </c>
       <c r="D87" t="s">
-        <v>160</v>
+        <v>967</v>
       </c>
       <c r="E87" t="s">
-        <v>161</v>
+        <v>1209</v>
       </c>
       <c r="F87" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G87" t="s">
         <v>873</v>
@@ -7119,13 +7131,13 @@
         <v>872</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D88" t="s">
-        <v>1477</v>
+        <v>160</v>
       </c>
       <c r="E88" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F88" t="s">
         <v>871</v>
@@ -7139,13 +7151,13 @@
         <v>872</v>
       </c>
       <c r="B89" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D89" t="s">
-        <v>165</v>
+        <v>1477</v>
       </c>
       <c r="E89" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F89" t="s">
         <v>871</v>
@@ -7158,14 +7170,17 @@
       <c r="A90" t="s">
         <v>872</v>
       </c>
+      <c r="B90" t="s">
+        <v>164</v>
+      </c>
       <c r="D90" t="s">
-        <v>1611</v>
+        <v>165</v>
       </c>
       <c r="E90" t="s">
-        <v>1612</v>
+        <v>166</v>
       </c>
       <c r="F90" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G90" t="s">
         <v>873</v>
@@ -7175,14 +7190,11 @@
       <c r="A91" t="s">
         <v>872</v>
       </c>
-      <c r="B91" t="s">
-        <v>968</v>
-      </c>
       <c r="D91" t="s">
-        <v>969</v>
+        <v>1611</v>
       </c>
       <c r="E91" t="s">
-        <v>1210</v>
+        <v>1612</v>
       </c>
       <c r="F91" t="s">
         <v>947</v>
@@ -7196,16 +7208,16 @@
         <v>872</v>
       </c>
       <c r="B92" t="s">
-        <v>169</v>
+        <v>968</v>
       </c>
       <c r="D92" t="s">
-        <v>170</v>
+        <v>969</v>
       </c>
       <c r="E92" t="s">
-        <v>171</v>
+        <v>1210</v>
       </c>
       <c r="F92" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G92" t="s">
         <v>873</v>
@@ -7216,13 +7228,13 @@
         <v>872</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D93" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E93" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F93" t="s">
         <v>871</v>
@@ -7236,16 +7248,16 @@
         <v>872</v>
       </c>
       <c r="B94" t="s">
-        <v>970</v>
+        <v>172</v>
       </c>
       <c r="D94" t="s">
-        <v>1211</v>
+        <v>173</v>
       </c>
       <c r="E94" t="s">
-        <v>1212</v>
+        <v>174</v>
       </c>
       <c r="F94" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G94" t="s">
         <v>873</v>
@@ -7256,16 +7268,13 @@
         <v>872</v>
       </c>
       <c r="B95" t="s">
-        <v>971</v>
-      </c>
-      <c r="C95" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D95" t="s">
-        <v>973</v>
+        <v>1211</v>
       </c>
       <c r="E95" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F95" t="s">
         <v>947</v>
@@ -7279,13 +7288,16 @@
         <v>872</v>
       </c>
       <c r="B96" t="s">
-        <v>974</v>
+        <v>971</v>
+      </c>
+      <c r="C96" t="s">
+        <v>972</v>
       </c>
       <c r="D96" t="s">
-        <v>1573</v>
+        <v>973</v>
       </c>
       <c r="E96" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="F96" t="s">
         <v>947</v>
@@ -7299,16 +7311,16 @@
         <v>872</v>
       </c>
       <c r="B97" t="s">
-        <v>1432</v>
+        <v>974</v>
       </c>
       <c r="D97" t="s">
-        <v>1433</v>
+        <v>1573</v>
       </c>
       <c r="E97" t="s">
-        <v>1434</v>
+        <v>1214</v>
       </c>
       <c r="F97" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G97" t="s">
         <v>873</v>
@@ -7319,13 +7331,13 @@
         <v>872</v>
       </c>
       <c r="B98" t="s">
-        <v>175</v>
+        <v>1432</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>1433</v>
       </c>
       <c r="E98" t="s">
-        <v>177</v>
+        <v>1434</v>
       </c>
       <c r="F98" t="s">
         <v>871</v>
@@ -7339,16 +7351,13 @@
         <v>872</v>
       </c>
       <c r="B99" t="s">
-        <v>837</v>
-      </c>
-      <c r="C99" t="s">
-        <v>838</v>
+        <v>175</v>
       </c>
       <c r="D99" t="s">
-        <v>839</v>
+        <v>176</v>
       </c>
       <c r="E99" t="s">
-        <v>840</v>
+        <v>177</v>
       </c>
       <c r="F99" t="s">
         <v>871</v>
@@ -7362,16 +7371,19 @@
         <v>872</v>
       </c>
       <c r="B100" t="s">
-        <v>1140</v>
+        <v>837</v>
+      </c>
+      <c r="C100" t="s">
+        <v>838</v>
       </c>
       <c r="D100" t="s">
-        <v>1129</v>
+        <v>839</v>
       </c>
       <c r="E100" t="s">
-        <v>1141</v>
+        <v>840</v>
       </c>
       <c r="F100" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G100" t="s">
         <v>873</v>
@@ -7382,16 +7394,16 @@
         <v>872</v>
       </c>
       <c r="B101" t="s">
-        <v>178</v>
+        <v>1140</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>1129</v>
       </c>
       <c r="E101" t="s">
-        <v>180</v>
+        <v>1141</v>
       </c>
       <c r="F101" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G101" t="s">
         <v>873</v>
@@ -7402,19 +7414,16 @@
         <v>872</v>
       </c>
       <c r="B102" t="s">
-        <v>975</v>
-      </c>
-      <c r="C102" t="s">
-        <v>976</v>
+        <v>178</v>
       </c>
       <c r="D102" t="s">
-        <v>977</v>
+        <v>179</v>
       </c>
       <c r="E102" t="s">
-        <v>1215</v>
+        <v>180</v>
       </c>
       <c r="F102" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G102" t="s">
         <v>873</v>
@@ -7425,16 +7434,19 @@
         <v>872</v>
       </c>
       <c r="B103" t="s">
-        <v>181</v>
+        <v>975</v>
+      </c>
+      <c r="C103" t="s">
+        <v>976</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>977</v>
       </c>
       <c r="E103" t="s">
-        <v>183</v>
+        <v>1215</v>
       </c>
       <c r="F103" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G103" t="s">
         <v>873</v>
@@ -7445,16 +7457,13 @@
         <v>872</v>
       </c>
       <c r="B104" t="s">
-        <v>841</v>
-      </c>
-      <c r="C104" t="s">
-        <v>842</v>
+        <v>181</v>
       </c>
       <c r="D104" t="s">
-        <v>843</v>
+        <v>182</v>
       </c>
       <c r="E104" t="s">
-        <v>844</v>
+        <v>183</v>
       </c>
       <c r="F104" t="s">
         <v>871</v>
@@ -7468,13 +7477,16 @@
         <v>872</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>841</v>
+      </c>
+      <c r="C105" t="s">
+        <v>842</v>
       </c>
       <c r="D105" t="s">
-        <v>188</v>
+        <v>843</v>
       </c>
       <c r="E105" t="s">
-        <v>189</v>
+        <v>844</v>
       </c>
       <c r="F105" t="s">
         <v>871</v>
@@ -7488,13 +7500,13 @@
         <v>872</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D106" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E106" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F106" t="s">
         <v>871</v>
@@ -7508,13 +7520,13 @@
         <v>872</v>
       </c>
       <c r="B107" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D107" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E107" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F107" t="s">
         <v>871</v>
@@ -7528,13 +7540,13 @@
         <v>872</v>
       </c>
       <c r="B108" t="s">
-        <v>849</v>
+        <v>193</v>
       </c>
       <c r="D108" t="s">
-        <v>1128</v>
+        <v>194</v>
       </c>
       <c r="E108" t="s">
-        <v>850</v>
+        <v>195</v>
       </c>
       <c r="F108" t="s">
         <v>871</v>
@@ -7548,19 +7560,19 @@
         <v>872</v>
       </c>
       <c r="B109" t="s">
-        <v>1557</v>
+        <v>849</v>
       </c>
       <c r="D109" t="s">
-        <v>1558</v>
+        <v>1128</v>
       </c>
       <c r="E109" t="s">
-        <v>1559</v>
+        <v>850</v>
       </c>
       <c r="F109" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G109" t="s">
-        <v>1556</v>
+        <v>873</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -7568,19 +7580,19 @@
         <v>872</v>
       </c>
       <c r="B110" t="s">
-        <v>198</v>
+        <v>1557</v>
       </c>
       <c r="D110" t="s">
-        <v>199</v>
+        <v>1558</v>
       </c>
       <c r="E110" t="s">
-        <v>200</v>
+        <v>1559</v>
       </c>
       <c r="F110" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G110" t="s">
-        <v>873</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -7588,16 +7600,16 @@
         <v>872</v>
       </c>
       <c r="B111" t="s">
-        <v>978</v>
+        <v>198</v>
       </c>
       <c r="D111" t="s">
-        <v>979</v>
+        <v>199</v>
       </c>
       <c r="E111" t="s">
-        <v>1218</v>
+        <v>200</v>
       </c>
       <c r="F111" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G111" t="s">
         <v>873</v>
@@ -7608,19 +7620,16 @@
         <v>872</v>
       </c>
       <c r="B112" t="s">
-        <v>1478</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1479</v>
+        <v>978</v>
       </c>
       <c r="D112" t="s">
-        <v>1480</v>
+        <v>979</v>
       </c>
       <c r="E112" t="s">
-        <v>1481</v>
+        <v>1218</v>
       </c>
       <c r="F112" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G112" t="s">
         <v>873</v>
@@ -7631,13 +7640,16 @@
         <v>872</v>
       </c>
       <c r="B113" t="s">
-        <v>201</v>
+        <v>1478</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1479</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>1480</v>
       </c>
       <c r="E113" t="s">
-        <v>203</v>
+        <v>1481</v>
       </c>
       <c r="F113" t="s">
         <v>871</v>
@@ -7651,16 +7663,16 @@
         <v>872</v>
       </c>
       <c r="B114" t="s">
-        <v>1613</v>
+        <v>201</v>
       </c>
       <c r="D114" t="s">
-        <v>1614</v>
+        <v>202</v>
       </c>
       <c r="E114" t="s">
-        <v>1615</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G114" t="s">
         <v>873</v>
@@ -7671,16 +7683,16 @@
         <v>872</v>
       </c>
       <c r="B115" t="s">
-        <v>204</v>
+        <v>1613</v>
       </c>
       <c r="D115" t="s">
-        <v>205</v>
+        <v>1614</v>
       </c>
       <c r="E115" t="s">
-        <v>206</v>
+        <v>1615</v>
       </c>
       <c r="F115" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G115" t="s">
         <v>873</v>
@@ -7691,16 +7703,16 @@
         <v>872</v>
       </c>
       <c r="B116" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D116" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E116" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F116" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G116" t="s">
         <v>873</v>
@@ -7711,16 +7723,16 @@
         <v>872</v>
       </c>
       <c r="B117" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D117" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E117" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F117" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G117" t="s">
         <v>873</v>
@@ -7731,13 +7743,13 @@
         <v>872</v>
       </c>
       <c r="B118" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D118" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E118" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F118" t="s">
         <v>871</v>
@@ -7751,16 +7763,16 @@
         <v>872</v>
       </c>
       <c r="B119" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D119" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E119" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F119" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G119" t="s">
         <v>873</v>
@@ -7771,13 +7783,13 @@
         <v>872</v>
       </c>
       <c r="B120" t="s">
-        <v>980</v>
+        <v>216</v>
       </c>
       <c r="D120" t="s">
-        <v>981</v>
+        <v>217</v>
       </c>
       <c r="E120" t="s">
-        <v>1219</v>
+        <v>218</v>
       </c>
       <c r="F120" t="s">
         <v>947</v>
@@ -7791,13 +7803,13 @@
         <v>872</v>
       </c>
       <c r="B121" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="D121" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="E121" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="F121" t="s">
         <v>947</v>
@@ -7811,13 +7823,13 @@
         <v>872</v>
       </c>
       <c r="B122" t="s">
-        <v>1435</v>
+        <v>982</v>
       </c>
       <c r="D122" t="s">
-        <v>1436</v>
+        <v>983</v>
       </c>
       <c r="E122" t="s">
-        <v>1437</v>
+        <v>1220</v>
       </c>
       <c r="F122" t="s">
         <v>947</v>
@@ -7831,16 +7843,16 @@
         <v>872</v>
       </c>
       <c r="B123" t="s">
-        <v>219</v>
+        <v>1435</v>
       </c>
       <c r="D123" t="s">
-        <v>220</v>
+        <v>1436</v>
       </c>
       <c r="E123" t="s">
-        <v>221</v>
+        <v>1437</v>
       </c>
       <c r="F123" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G123" t="s">
         <v>873</v>
@@ -7851,16 +7863,16 @@
         <v>872</v>
       </c>
       <c r="B124" t="s">
-        <v>1142</v>
+        <v>219</v>
       </c>
       <c r="D124" t="s">
-        <v>1127</v>
+        <v>220</v>
       </c>
       <c r="E124" t="s">
-        <v>1143</v>
+        <v>221</v>
       </c>
       <c r="F124" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G124" t="s">
         <v>873</v>
@@ -7891,19 +7903,16 @@
         <v>872</v>
       </c>
       <c r="B126" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C126" t="s">
-        <v>940</v>
+        <v>1142</v>
       </c>
       <c r="D126" t="s">
-        <v>1222</v>
+        <v>1127</v>
       </c>
       <c r="E126" t="s">
-        <v>1223</v>
+        <v>1143</v>
       </c>
       <c r="F126" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G126" t="s">
         <v>873</v>
@@ -7914,13 +7923,16 @@
         <v>872</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>1221</v>
+      </c>
+      <c r="C127" t="s">
+        <v>940</v>
       </c>
       <c r="D127" t="s">
-        <v>223</v>
+        <v>1222</v>
       </c>
       <c r="E127" t="s">
-        <v>224</v>
+        <v>1223</v>
       </c>
       <c r="F127" t="s">
         <v>871</v>
@@ -7934,16 +7946,13 @@
         <v>872</v>
       </c>
       <c r="B128" t="s">
-        <v>881</v>
-      </c>
-      <c r="C128" t="s">
-        <v>882</v>
+        <v>222</v>
       </c>
       <c r="D128" t="s">
-        <v>1224</v>
+        <v>223</v>
       </c>
       <c r="E128" t="s">
-        <v>883</v>
+        <v>224</v>
       </c>
       <c r="F128" t="s">
         <v>871</v>
@@ -7957,13 +7966,16 @@
         <v>872</v>
       </c>
       <c r="B129" t="s">
-        <v>1619</v>
+        <v>881</v>
+      </c>
+      <c r="C129" t="s">
+        <v>882</v>
       </c>
       <c r="D129" t="s">
-        <v>1620</v>
+        <v>1224</v>
       </c>
       <c r="E129" t="s">
-        <v>1621</v>
+        <v>883</v>
       </c>
       <c r="F129" t="s">
         <v>871</v>
@@ -7997,13 +8009,13 @@
         <v>872</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>1619</v>
       </c>
       <c r="D131" t="s">
-        <v>226</v>
+        <v>1620</v>
       </c>
       <c r="E131" t="s">
-        <v>227</v>
+        <v>1621</v>
       </c>
       <c r="F131" t="s">
         <v>871</v>
@@ -8017,13 +8029,13 @@
         <v>872</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D132" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E132" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F132" t="s">
         <v>871</v>
@@ -8037,16 +8049,13 @@
         <v>872</v>
       </c>
       <c r="B133" t="s">
-        <v>877</v>
-      </c>
-      <c r="C133" t="s">
-        <v>878</v>
+        <v>228</v>
       </c>
       <c r="D133" t="s">
-        <v>879</v>
+        <v>229</v>
       </c>
       <c r="E133" t="s">
-        <v>880</v>
+        <v>230</v>
       </c>
       <c r="F133" t="s">
         <v>871</v>
@@ -8060,16 +8069,19 @@
         <v>872</v>
       </c>
       <c r="B134" t="s">
-        <v>1144</v>
+        <v>877</v>
+      </c>
+      <c r="C134" t="s">
+        <v>878</v>
       </c>
       <c r="D134" t="s">
-        <v>1112</v>
+        <v>879</v>
       </c>
       <c r="E134" t="s">
-        <v>1145</v>
+        <v>880</v>
       </c>
       <c r="F134" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G134" t="s">
         <v>873</v>
@@ -8080,16 +8092,16 @@
         <v>872</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>1144</v>
       </c>
       <c r="D135" t="s">
-        <v>232</v>
+        <v>1112</v>
       </c>
       <c r="E135" t="s">
-        <v>233</v>
+        <v>1145</v>
       </c>
       <c r="F135" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G135" t="s">
         <v>873</v>
@@ -8100,13 +8112,13 @@
         <v>872</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D136" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E136" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F136" t="s">
         <v>871</v>
@@ -8120,13 +8132,13 @@
         <v>872</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D137" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E137" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F137" t="s">
         <v>871</v>
@@ -8140,16 +8152,16 @@
         <v>872</v>
       </c>
       <c r="B138" t="s">
-        <v>1622</v>
+        <v>237</v>
       </c>
       <c r="D138" t="s">
-        <v>1623</v>
+        <v>238</v>
       </c>
       <c r="E138" t="s">
-        <v>1624</v>
+        <v>239</v>
       </c>
       <c r="F138" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G138" t="s">
         <v>873</v>
@@ -8160,16 +8172,16 @@
         <v>872</v>
       </c>
       <c r="B139" t="s">
-        <v>1228</v>
+        <v>1622</v>
       </c>
       <c r="D139" t="s">
-        <v>1229</v>
+        <v>1623</v>
       </c>
       <c r="E139" t="s">
-        <v>1230</v>
+        <v>1624</v>
       </c>
       <c r="F139" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G139" t="s">
         <v>873</v>
@@ -8180,16 +8192,16 @@
         <v>872</v>
       </c>
       <c r="B140" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="D140" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="E140" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="F140" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G140" t="s">
         <v>873</v>
@@ -8200,13 +8212,13 @@
         <v>872</v>
       </c>
       <c r="B141" t="s">
-        <v>984</v>
+        <v>1231</v>
       </c>
       <c r="D141" t="s">
-        <v>985</v>
+        <v>1232</v>
       </c>
       <c r="E141" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F141" t="s">
         <v>947</v>
@@ -8220,13 +8232,13 @@
         <v>872</v>
       </c>
       <c r="B142" t="s">
-        <v>1235</v>
+        <v>984</v>
       </c>
       <c r="D142" t="s">
-        <v>1236</v>
+        <v>985</v>
       </c>
       <c r="E142" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="F142" t="s">
         <v>947</v>
@@ -8240,13 +8252,13 @@
         <v>872</v>
       </c>
       <c r="B143" t="s">
-        <v>986</v>
+        <v>1235</v>
       </c>
       <c r="D143" t="s">
-        <v>987</v>
+        <v>1236</v>
       </c>
       <c r="E143" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="F143" t="s">
         <v>947</v>
@@ -8260,16 +8272,16 @@
         <v>872</v>
       </c>
       <c r="B144" t="s">
-        <v>240</v>
+        <v>986</v>
       </c>
       <c r="D144" t="s">
-        <v>241</v>
+        <v>987</v>
       </c>
       <c r="E144" t="s">
-        <v>242</v>
+        <v>1238</v>
       </c>
       <c r="F144" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G144" t="s">
         <v>873</v>
@@ -8280,16 +8292,16 @@
         <v>872</v>
       </c>
       <c r="B145" t="s">
-        <v>1146</v>
+        <v>240</v>
       </c>
       <c r="D145" t="s">
-        <v>1113</v>
+        <v>241</v>
       </c>
       <c r="E145" t="s">
-        <v>1147</v>
+        <v>242</v>
       </c>
       <c r="F145" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G145" t="s">
         <v>873</v>
@@ -8300,13 +8312,13 @@
         <v>872</v>
       </c>
       <c r="B146" t="s">
-        <v>243</v>
+        <v>1146</v>
       </c>
       <c r="D146" t="s">
-        <v>244</v>
+        <v>1113</v>
       </c>
       <c r="E146" t="s">
-        <v>245</v>
+        <v>1147</v>
       </c>
       <c r="F146" t="s">
         <v>947</v>
@@ -8320,16 +8332,16 @@
         <v>872</v>
       </c>
       <c r="B147" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D147" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E147" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F147" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G147" t="s">
         <v>873</v>
@@ -8340,16 +8352,16 @@
         <v>872</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D148" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E148" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F148" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G148" t="s">
         <v>873</v>
@@ -8360,13 +8372,13 @@
         <v>872</v>
       </c>
       <c r="B149" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D149" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E149" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F149" t="s">
         <v>947</v>
@@ -8380,19 +8392,16 @@
         <v>872</v>
       </c>
       <c r="B150" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C150" t="s">
-        <v>1483</v>
+        <v>252</v>
       </c>
       <c r="D150" t="s">
-        <v>1484</v>
+        <v>253</v>
       </c>
       <c r="E150" t="s">
-        <v>1485</v>
+        <v>254</v>
       </c>
       <c r="F150" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G150" t="s">
         <v>873</v>
@@ -8403,19 +8412,19 @@
         <v>872</v>
       </c>
       <c r="B151" t="s">
-        <v>988</v>
+        <v>1482</v>
       </c>
       <c r="C151" t="s">
-        <v>989</v>
+        <v>1483</v>
       </c>
       <c r="D151" t="s">
-        <v>990</v>
+        <v>1484</v>
       </c>
       <c r="E151" t="s">
-        <v>1239</v>
+        <v>1485</v>
       </c>
       <c r="F151" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G151" t="s">
         <v>873</v>
@@ -8426,16 +8435,19 @@
         <v>872</v>
       </c>
       <c r="B152" t="s">
-        <v>255</v>
+        <v>988</v>
+      </c>
+      <c r="C152" t="s">
+        <v>989</v>
       </c>
       <c r="D152" t="s">
-        <v>256</v>
+        <v>990</v>
       </c>
       <c r="E152" t="s">
-        <v>257</v>
+        <v>1239</v>
       </c>
       <c r="F152" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G152" t="s">
         <v>873</v>
@@ -8446,13 +8458,13 @@
         <v>872</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D153" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E153" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F153" t="s">
         <v>871</v>
@@ -8466,13 +8478,13 @@
         <v>872</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D154" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E154" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F154" t="s">
         <v>871</v>
@@ -8486,13 +8498,13 @@
         <v>872</v>
       </c>
       <c r="B155" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D155" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E155" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F155" t="s">
         <v>871</v>
@@ -8506,16 +8518,16 @@
         <v>872</v>
       </c>
       <c r="B156" t="s">
-        <v>991</v>
+        <v>264</v>
       </c>
       <c r="D156" t="s">
-        <v>1240</v>
+        <v>265</v>
       </c>
       <c r="E156" t="s">
-        <v>1241</v>
+        <v>266</v>
       </c>
       <c r="F156" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G156" t="s">
         <v>873</v>
@@ -8526,13 +8538,13 @@
         <v>872</v>
       </c>
       <c r="B157" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D157" t="s">
-        <v>993</v>
+        <v>1240</v>
       </c>
       <c r="E157" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F157" t="s">
         <v>947</v>
@@ -8546,16 +8558,16 @@
         <v>872</v>
       </c>
       <c r="B158" t="s">
-        <v>887</v>
+        <v>992</v>
       </c>
       <c r="D158" t="s">
-        <v>888</v>
+        <v>993</v>
       </c>
       <c r="E158" t="s">
-        <v>889</v>
+        <v>1242</v>
       </c>
       <c r="F158" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G158" t="s">
         <v>873</v>
@@ -8566,16 +8578,16 @@
         <v>872</v>
       </c>
       <c r="B159" t="s">
-        <v>994</v>
+        <v>887</v>
       </c>
       <c r="D159" t="s">
-        <v>995</v>
+        <v>888</v>
       </c>
       <c r="E159" t="s">
-        <v>1243</v>
+        <v>889</v>
       </c>
       <c r="F159" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G159" t="s">
         <v>873</v>
@@ -8586,13 +8598,13 @@
         <v>872</v>
       </c>
       <c r="B160" t="s">
-        <v>1438</v>
+        <v>994</v>
       </c>
       <c r="D160" t="s">
-        <v>1439</v>
+        <v>995</v>
       </c>
       <c r="E160" t="s">
-        <v>1440</v>
+        <v>1243</v>
       </c>
       <c r="F160" t="s">
         <v>947</v>
@@ -8606,13 +8618,13 @@
         <v>872</v>
       </c>
       <c r="B161" t="s">
-        <v>267</v>
+        <v>1438</v>
       </c>
       <c r="D161" t="s">
-        <v>268</v>
+        <v>1439</v>
       </c>
       <c r="E161" t="s">
-        <v>269</v>
+        <v>1440</v>
       </c>
       <c r="F161" t="s">
         <v>947</v>
@@ -8626,16 +8638,16 @@
         <v>872</v>
       </c>
       <c r="B162" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E162" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F162" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G162" t="s">
         <v>873</v>
@@ -8646,16 +8658,16 @@
         <v>872</v>
       </c>
       <c r="B163" t="s">
-        <v>996</v>
+        <v>270</v>
       </c>
       <c r="D163" t="s">
-        <v>997</v>
+        <v>271</v>
       </c>
       <c r="E163" t="s">
-        <v>1244</v>
+        <v>272</v>
       </c>
       <c r="F163" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G163" t="s">
         <v>873</v>
@@ -8666,13 +8678,13 @@
         <v>872</v>
       </c>
       <c r="B164" t="s">
-        <v>1625</v>
+        <v>996</v>
       </c>
       <c r="D164" t="s">
-        <v>1626</v>
+        <v>997</v>
       </c>
       <c r="E164" t="s">
-        <v>1627</v>
+        <v>1244</v>
       </c>
       <c r="F164" t="s">
         <v>947</v>
@@ -8686,13 +8698,13 @@
         <v>872</v>
       </c>
       <c r="B165" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="D165" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="E165" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="F165" t="s">
         <v>947</v>
@@ -8706,13 +8718,13 @@
         <v>872</v>
       </c>
       <c r="B166" t="s">
-        <v>1148</v>
+        <v>1628</v>
       </c>
       <c r="D166" t="s">
-        <v>1115</v>
+        <v>1629</v>
       </c>
       <c r="E166" t="s">
-        <v>1149</v>
+        <v>1630</v>
       </c>
       <c r="F166" t="s">
         <v>947</v>
@@ -8726,16 +8738,16 @@
         <v>872</v>
       </c>
       <c r="B167" t="s">
-        <v>275</v>
+        <v>1148</v>
       </c>
       <c r="D167" t="s">
-        <v>276</v>
+        <v>1115</v>
       </c>
       <c r="E167" t="s">
-        <v>277</v>
+        <v>1149</v>
       </c>
       <c r="F167" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G167" t="s">
         <v>873</v>
@@ -8746,13 +8758,13 @@
         <v>872</v>
       </c>
       <c r="B168" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D168" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E168" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F168" t="s">
         <v>871</v>
@@ -8766,16 +8778,16 @@
         <v>872</v>
       </c>
       <c r="B169" t="s">
-        <v>1441</v>
+        <v>278</v>
       </c>
       <c r="D169" t="s">
-        <v>1442</v>
+        <v>279</v>
       </c>
       <c r="E169" t="s">
-        <v>1443</v>
+        <v>280</v>
       </c>
       <c r="F169" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G169" t="s">
         <v>873</v>
@@ -8786,16 +8798,16 @@
         <v>872</v>
       </c>
       <c r="B170" t="s">
-        <v>281</v>
+        <v>1441</v>
       </c>
       <c r="D170" t="s">
-        <v>282</v>
+        <v>1442</v>
       </c>
       <c r="E170" t="s">
-        <v>197</v>
+        <v>1443</v>
       </c>
       <c r="F170" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G170" t="s">
         <v>873</v>
@@ -8806,16 +8818,16 @@
         <v>872</v>
       </c>
       <c r="B171" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D171" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E171" t="s">
-        <v>285</v>
+        <v>197</v>
       </c>
       <c r="F171" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G171" t="s">
         <v>873</v>
@@ -8826,13 +8838,13 @@
         <v>872</v>
       </c>
       <c r="B172" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D172" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E172" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F172" t="s">
         <v>947</v>
@@ -8846,16 +8858,16 @@
         <v>872</v>
       </c>
       <c r="B173" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D173" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E173" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F173" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G173" t="s">
         <v>873</v>
@@ -8866,13 +8878,13 @@
         <v>872</v>
       </c>
       <c r="B174" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D174" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E174" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F174" t="s">
         <v>871</v>
@@ -8886,13 +8898,13 @@
         <v>872</v>
       </c>
       <c r="B175" t="s">
-        <v>1245</v>
+        <v>292</v>
       </c>
       <c r="D175" t="s">
-        <v>1246</v>
+        <v>293</v>
       </c>
       <c r="E175" t="s">
-        <v>1247</v>
+        <v>294</v>
       </c>
       <c r="F175" t="s">
         <v>871</v>
@@ -8906,16 +8918,16 @@
         <v>872</v>
       </c>
       <c r="B176" t="s">
-        <v>1150</v>
+        <v>1245</v>
       </c>
       <c r="D176" t="s">
-        <v>1130</v>
+        <v>1246</v>
       </c>
       <c r="E176" t="s">
-        <v>1151</v>
+        <v>1247</v>
       </c>
       <c r="F176" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G176" t="s">
         <v>873</v>
@@ -8926,16 +8938,16 @@
         <v>872</v>
       </c>
       <c r="B177" t="s">
-        <v>295</v>
+        <v>1150</v>
       </c>
       <c r="D177" t="s">
-        <v>296</v>
+        <v>1130</v>
       </c>
       <c r="E177" t="s">
-        <v>297</v>
+        <v>1151</v>
       </c>
       <c r="F177" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G177" t="s">
         <v>873</v>
@@ -8946,13 +8958,13 @@
         <v>872</v>
       </c>
       <c r="B178" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D178" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E178" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F178" t="s">
         <v>871</v>
@@ -8966,13 +8978,13 @@
         <v>872</v>
       </c>
       <c r="B179" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D179" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E179" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F179" t="s">
         <v>871</v>
@@ -8986,16 +8998,16 @@
         <v>872</v>
       </c>
       <c r="B180" t="s">
-        <v>998</v>
+        <v>301</v>
       </c>
       <c r="D180" t="s">
-        <v>999</v>
+        <v>302</v>
       </c>
       <c r="E180" t="s">
-        <v>1248</v>
+        <v>303</v>
       </c>
       <c r="F180" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G180" t="s">
         <v>873</v>
@@ -9006,16 +9018,16 @@
         <v>872</v>
       </c>
       <c r="B181" t="s">
-        <v>304</v>
+        <v>998</v>
       </c>
       <c r="D181" t="s">
-        <v>305</v>
+        <v>999</v>
       </c>
       <c r="E181" t="s">
-        <v>306</v>
+        <v>1248</v>
       </c>
       <c r="F181" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G181" t="s">
         <v>873</v>
@@ -9026,13 +9038,13 @@
         <v>872</v>
       </c>
       <c r="B182" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D182" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E182" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F182" t="s">
         <v>871</v>
@@ -9046,16 +9058,16 @@
         <v>872</v>
       </c>
       <c r="B183" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D183" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E183" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F183" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G183" t="s">
         <v>873</v>
@@ -9066,19 +9078,16 @@
         <v>872</v>
       </c>
       <c r="B184" t="s">
-        <v>859</v>
-      </c>
-      <c r="C184" t="s">
-        <v>860</v>
+        <v>310</v>
       </c>
       <c r="D184" t="s">
-        <v>861</v>
+        <v>311</v>
       </c>
       <c r="E184" t="s">
-        <v>862</v>
+        <v>312</v>
       </c>
       <c r="F184" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G184" t="s">
         <v>873</v>
@@ -9089,16 +9098,19 @@
         <v>872</v>
       </c>
       <c r="B185" t="s">
-        <v>1152</v>
+        <v>859</v>
+      </c>
+      <c r="C185" t="s">
+        <v>860</v>
       </c>
       <c r="D185" t="s">
-        <v>1131</v>
+        <v>861</v>
       </c>
       <c r="E185" t="s">
-        <v>1153</v>
+        <v>862</v>
       </c>
       <c r="F185" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G185" t="s">
         <v>873</v>
@@ -9109,19 +9121,16 @@
         <v>872</v>
       </c>
       <c r="B186" t="s">
-        <v>313</v>
-      </c>
-      <c r="C186" t="s">
-        <v>314</v>
+        <v>1152</v>
       </c>
       <c r="D186" t="s">
-        <v>1249</v>
+        <v>1131</v>
       </c>
       <c r="E186" t="s">
-        <v>315</v>
+        <v>1153</v>
       </c>
       <c r="F186" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G186" t="s">
         <v>873</v>
@@ -9132,13 +9141,16 @@
         <v>872</v>
       </c>
       <c r="B187" t="s">
-        <v>316</v>
+        <v>313</v>
+      </c>
+      <c r="C187" t="s">
+        <v>314</v>
       </c>
       <c r="D187" t="s">
-        <v>317</v>
+        <v>1249</v>
       </c>
       <c r="E187" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F187" t="s">
         <v>871</v>
@@ -9152,13 +9164,13 @@
         <v>872</v>
       </c>
       <c r="B188" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D188" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E188" t="s">
-        <v>1250</v>
+        <v>318</v>
       </c>
       <c r="F188" t="s">
         <v>871</v>
@@ -9172,13 +9184,13 @@
         <v>872</v>
       </c>
       <c r="B189" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D189" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E189" t="s">
-        <v>323</v>
+        <v>1250</v>
       </c>
       <c r="F189" t="s">
         <v>871</v>
@@ -9192,16 +9204,16 @@
         <v>872</v>
       </c>
       <c r="B190" t="s">
-        <v>1486</v>
+        <v>321</v>
       </c>
       <c r="D190" t="s">
-        <v>1487</v>
+        <v>322</v>
       </c>
       <c r="E190" t="s">
-        <v>1488</v>
+        <v>323</v>
       </c>
       <c r="F190" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G190" t="s">
         <v>873</v>
@@ -9212,13 +9224,13 @@
         <v>872</v>
       </c>
       <c r="B191" t="s">
-        <v>1000</v>
+        <v>1486</v>
       </c>
       <c r="D191" t="s">
-        <v>1251</v>
+        <v>1487</v>
       </c>
       <c r="E191" t="s">
-        <v>1252</v>
+        <v>1488</v>
       </c>
       <c r="F191" t="s">
         <v>947</v>
@@ -9232,13 +9244,13 @@
         <v>872</v>
       </c>
       <c r="B192" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D192" t="s">
-        <v>1002</v>
+        <v>1251</v>
       </c>
       <c r="E192" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F192" t="s">
         <v>947</v>
@@ -9252,16 +9264,16 @@
         <v>872</v>
       </c>
       <c r="B193" t="s">
-        <v>324</v>
+        <v>1001</v>
       </c>
       <c r="D193" t="s">
-        <v>325</v>
+        <v>1002</v>
       </c>
       <c r="E193" t="s">
-        <v>326</v>
+        <v>1253</v>
       </c>
       <c r="F193" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G193" t="s">
         <v>873</v>
@@ -9272,13 +9284,13 @@
         <v>872</v>
       </c>
       <c r="B194" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D194" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E194" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F194" t="s">
         <v>871</v>
@@ -9292,13 +9304,13 @@
         <v>872</v>
       </c>
       <c r="B195" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D195" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E195" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F195" t="s">
         <v>871</v>
@@ -9312,13 +9324,13 @@
         <v>872</v>
       </c>
       <c r="B196" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D196" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E196" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F196" t="s">
         <v>871</v>
@@ -9332,16 +9344,16 @@
         <v>872</v>
       </c>
       <c r="B197" t="s">
-        <v>1003</v>
+        <v>333</v>
       </c>
       <c r="D197" t="s">
-        <v>1004</v>
+        <v>334</v>
       </c>
       <c r="E197" t="s">
-        <v>1254</v>
+        <v>335</v>
       </c>
       <c r="F197" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G197" t="s">
         <v>873</v>
@@ -9352,16 +9364,16 @@
         <v>872</v>
       </c>
       <c r="B198" t="s">
-        <v>336</v>
+        <v>1003</v>
       </c>
       <c r="D198" t="s">
-        <v>337</v>
+        <v>1004</v>
       </c>
       <c r="E198" t="s">
-        <v>338</v>
+        <v>1254</v>
       </c>
       <c r="F198" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G198" t="s">
         <v>873</v>
@@ -9372,16 +9384,13 @@
         <v>872</v>
       </c>
       <c r="B199" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1490</v>
+        <v>336</v>
       </c>
       <c r="D199" t="s">
-        <v>1491</v>
+        <v>337</v>
       </c>
       <c r="E199" t="s">
-        <v>1492</v>
+        <v>338</v>
       </c>
       <c r="F199" t="s">
         <v>871</v>
@@ -9395,13 +9404,16 @@
         <v>872</v>
       </c>
       <c r="B200" t="s">
-        <v>339</v>
+        <v>1489</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1490</v>
       </c>
       <c r="D200" t="s">
-        <v>340</v>
+        <v>1491</v>
       </c>
       <c r="E200" t="s">
-        <v>341</v>
+        <v>1492</v>
       </c>
       <c r="F200" t="s">
         <v>871</v>
@@ -9415,13 +9427,13 @@
         <v>872</v>
       </c>
       <c r="B201" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D201" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E201" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F201" t="s">
         <v>871</v>
@@ -9435,16 +9447,16 @@
         <v>872</v>
       </c>
       <c r="B202" t="s">
-        <v>1005</v>
+        <v>342</v>
       </c>
       <c r="D202" t="s">
-        <v>1006</v>
+        <v>343</v>
       </c>
       <c r="E202" t="s">
-        <v>1255</v>
+        <v>344</v>
       </c>
       <c r="F202" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G202" t="s">
         <v>873</v>
@@ -9455,13 +9467,13 @@
         <v>872</v>
       </c>
       <c r="B203" t="s">
-        <v>1256</v>
+        <v>1005</v>
       </c>
       <c r="D203" t="s">
-        <v>1257</v>
+        <v>1006</v>
       </c>
       <c r="E203" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="F203" t="s">
         <v>947</v>
@@ -9475,16 +9487,16 @@
         <v>872</v>
       </c>
       <c r="B204" t="s">
-        <v>345</v>
+        <v>1256</v>
       </c>
       <c r="D204" t="s">
-        <v>346</v>
+        <v>1257</v>
       </c>
       <c r="E204" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F204" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G204" t="s">
         <v>873</v>
@@ -9495,19 +9507,16 @@
         <v>872</v>
       </c>
       <c r="B205" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1008</v>
+        <v>345</v>
       </c>
       <c r="D205" t="s">
-        <v>1260</v>
+        <v>346</v>
       </c>
       <c r="E205" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="F205" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G205" t="s">
         <v>873</v>
@@ -9518,16 +9527,19 @@
         <v>872</v>
       </c>
       <c r="B206" t="s">
-        <v>347</v>
+        <v>1007</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1008</v>
       </c>
       <c r="D206" t="s">
-        <v>348</v>
+        <v>1260</v>
       </c>
       <c r="E206" t="s">
-        <v>349</v>
+        <v>1261</v>
       </c>
       <c r="F206" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G206" t="s">
         <v>873</v>
@@ -9538,13 +9550,13 @@
         <v>872</v>
       </c>
       <c r="B207" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D207" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E207" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F207" t="s">
         <v>871</v>
@@ -9558,19 +9570,16 @@
         <v>872</v>
       </c>
       <c r="B208" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C208" t="s">
-        <v>1010</v>
+        <v>350</v>
       </c>
       <c r="D208" t="s">
-        <v>1011</v>
+        <v>351</v>
       </c>
       <c r="E208" t="s">
-        <v>1262</v>
+        <v>352</v>
       </c>
       <c r="F208" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G208" t="s">
         <v>873</v>
@@ -9581,16 +9590,19 @@
         <v>872</v>
       </c>
       <c r="B209" t="s">
-        <v>353</v>
+        <v>1009</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1010</v>
       </c>
       <c r="D209" t="s">
-        <v>354</v>
+        <v>1011</v>
       </c>
       <c r="E209" t="s">
-        <v>355</v>
+        <v>1262</v>
       </c>
       <c r="F209" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G209" t="s">
         <v>873</v>
@@ -9601,13 +9613,13 @@
         <v>872</v>
       </c>
       <c r="B210" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D210" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E210" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F210" t="s">
         <v>871</v>
@@ -9621,13 +9633,13 @@
         <v>872</v>
       </c>
       <c r="B211" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D211" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E211" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F211" t="s">
         <v>871</v>
@@ -9641,13 +9653,13 @@
         <v>872</v>
       </c>
       <c r="B212" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F212" t="s">
         <v>871</v>
@@ -9661,19 +9673,16 @@
         <v>872</v>
       </c>
       <c r="B213" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C213" t="s">
-        <v>1494</v>
+        <v>362</v>
       </c>
       <c r="D213" t="s">
-        <v>1495</v>
+        <v>363</v>
       </c>
       <c r="E213" t="s">
-        <v>1496</v>
+        <v>364</v>
       </c>
       <c r="F213" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G213" t="s">
         <v>873</v>
@@ -9684,16 +9693,19 @@
         <v>872</v>
       </c>
       <c r="B214" t="s">
-        <v>365</v>
+        <v>1493</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1494</v>
       </c>
       <c r="D214" t="s">
-        <v>366</v>
+        <v>1495</v>
       </c>
       <c r="E214" t="s">
-        <v>367</v>
+        <v>1496</v>
       </c>
       <c r="F214" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G214" t="s">
         <v>873</v>
@@ -9704,13 +9716,13 @@
         <v>872</v>
       </c>
       <c r="B215" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D215" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E215" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F215" t="s">
         <v>871</v>
@@ -9724,13 +9736,13 @@
         <v>872</v>
       </c>
       <c r="B216" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D216" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E216" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F216" t="s">
         <v>871</v>
@@ -9744,19 +9756,16 @@
         <v>872</v>
       </c>
       <c r="B217" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C217" t="s">
-        <v>1013</v>
+        <v>371</v>
       </c>
       <c r="D217" t="s">
-        <v>1014</v>
+        <v>372</v>
       </c>
       <c r="E217" t="s">
-        <v>1263</v>
+        <v>373</v>
       </c>
       <c r="F217" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G217" t="s">
         <v>873</v>
@@ -9767,19 +9776,19 @@
         <v>872</v>
       </c>
       <c r="B218" t="s">
-        <v>901</v>
+        <v>1012</v>
       </c>
       <c r="C218" t="s">
-        <v>902</v>
+        <v>1013</v>
       </c>
       <c r="D218" t="s">
-        <v>1264</v>
+        <v>1014</v>
       </c>
       <c r="E218" t="s">
-        <v>903</v>
+        <v>1263</v>
       </c>
       <c r="F218" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G218" t="s">
         <v>873</v>
@@ -9790,13 +9799,16 @@
         <v>872</v>
       </c>
       <c r="B219" t="s">
-        <v>374</v>
+        <v>901</v>
+      </c>
+      <c r="C219" t="s">
+        <v>902</v>
       </c>
       <c r="D219" t="s">
-        <v>375</v>
+        <v>1264</v>
       </c>
       <c r="E219" t="s">
-        <v>376</v>
+        <v>903</v>
       </c>
       <c r="F219" t="s">
         <v>871</v>
@@ -9810,13 +9822,13 @@
         <v>872</v>
       </c>
       <c r="B220" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D220" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E220" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F220" t="s">
         <v>871</v>
@@ -9830,13 +9842,13 @@
         <v>872</v>
       </c>
       <c r="B221" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D221" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E221" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F221" t="s">
         <v>871</v>
@@ -9850,13 +9862,13 @@
         <v>872</v>
       </c>
       <c r="B222" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D222" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E222" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F222" t="s">
         <v>871</v>
@@ -9870,13 +9882,13 @@
         <v>872</v>
       </c>
       <c r="B223" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D223" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E223" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F223" t="s">
         <v>871</v>
@@ -9890,13 +9902,13 @@
         <v>872</v>
       </c>
       <c r="B224" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D224" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E224" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F224" t="s">
         <v>871</v>
@@ -9910,13 +9922,13 @@
         <v>872</v>
       </c>
       <c r="B225" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D225" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E225" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F225" t="s">
         <v>871</v>
@@ -9930,13 +9942,13 @@
         <v>872</v>
       </c>
       <c r="B226" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D226" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E226" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F226" t="s">
         <v>871</v>
@@ -9950,13 +9962,13 @@
         <v>872</v>
       </c>
       <c r="B227" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D227" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E227" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F227" t="s">
         <v>871</v>
@@ -9970,16 +9982,13 @@
         <v>872</v>
       </c>
       <c r="B228" t="s">
-        <v>927</v>
-      </c>
-      <c r="C228" t="s">
-        <v>941</v>
+        <v>398</v>
       </c>
       <c r="D228" t="s">
-        <v>916</v>
+        <v>399</v>
       </c>
       <c r="E228" t="s">
-        <v>1265</v>
+        <v>400</v>
       </c>
       <c r="F228" t="s">
         <v>871</v>
@@ -9993,16 +10002,19 @@
         <v>872</v>
       </c>
       <c r="B229" t="s">
-        <v>1444</v>
+        <v>927</v>
+      </c>
+      <c r="C229" t="s">
+        <v>941</v>
       </c>
       <c r="D229" t="s">
-        <v>1445</v>
+        <v>916</v>
       </c>
       <c r="E229" t="s">
-        <v>1446</v>
+        <v>1265</v>
       </c>
       <c r="F229" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G229" t="s">
         <v>873</v>
@@ -10013,13 +10025,13 @@
         <v>872</v>
       </c>
       <c r="B230" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="D230" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="E230" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="F230" t="s">
         <v>947</v>
@@ -10033,13 +10045,13 @@
         <v>872</v>
       </c>
       <c r="B231" t="s">
-        <v>1016</v>
+        <v>1447</v>
       </c>
       <c r="D231" t="s">
-        <v>1497</v>
+        <v>1448</v>
       </c>
       <c r="E231" t="s">
-        <v>1266</v>
+        <v>1449</v>
       </c>
       <c r="F231" t="s">
         <v>947</v>
@@ -10053,13 +10065,13 @@
         <v>872</v>
       </c>
       <c r="B232" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D232" t="s">
-        <v>1018</v>
+        <v>1497</v>
       </c>
       <c r="E232" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="F232" t="s">
         <v>947</v>
@@ -10073,16 +10085,16 @@
         <v>872</v>
       </c>
       <c r="B233" t="s">
-        <v>401</v>
+        <v>1017</v>
       </c>
       <c r="D233" t="s">
-        <v>402</v>
+        <v>1018</v>
       </c>
       <c r="E233" t="s">
-        <v>403</v>
+        <v>1267</v>
       </c>
       <c r="F233" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G233" t="s">
         <v>873</v>
@@ -10093,16 +10105,16 @@
         <v>872</v>
       </c>
       <c r="B234" t="s">
-        <v>1450</v>
+        <v>401</v>
       </c>
       <c r="D234" t="s">
-        <v>1451</v>
+        <v>402</v>
       </c>
       <c r="E234" t="s">
-        <v>1452</v>
+        <v>403</v>
       </c>
       <c r="F234" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G234" t="s">
         <v>873</v>
@@ -10113,13 +10125,13 @@
         <v>872</v>
       </c>
       <c r="B235" t="s">
-        <v>1268</v>
+        <v>1450</v>
       </c>
       <c r="D235" t="s">
-        <v>1269</v>
+        <v>1451</v>
       </c>
       <c r="E235" t="s">
-        <v>1270</v>
+        <v>1452</v>
       </c>
       <c r="F235" t="s">
         <v>947</v>
@@ -10133,16 +10145,16 @@
         <v>872</v>
       </c>
       <c r="B236" t="s">
-        <v>1574</v>
+        <v>1268</v>
       </c>
       <c r="D236" t="s">
-        <v>1575</v>
+        <v>1269</v>
       </c>
       <c r="E236" t="s">
-        <v>1576</v>
+        <v>1270</v>
       </c>
       <c r="F236" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G236" t="s">
         <v>873</v>
@@ -10153,16 +10165,16 @@
         <v>872</v>
       </c>
       <c r="B237" t="s">
-        <v>1019</v>
+        <v>1574</v>
       </c>
       <c r="D237" t="s">
-        <v>1020</v>
+        <v>1575</v>
       </c>
       <c r="E237" t="s">
-        <v>1271</v>
+        <v>1576</v>
       </c>
       <c r="F237" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G237" t="s">
         <v>873</v>
@@ -10173,16 +10185,16 @@
         <v>872</v>
       </c>
       <c r="B238" t="s">
-        <v>406</v>
+        <v>1019</v>
       </c>
       <c r="D238" t="s">
-        <v>407</v>
+        <v>1020</v>
       </c>
       <c r="E238" t="s">
-        <v>408</v>
+        <v>1271</v>
       </c>
       <c r="F238" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G238" t="s">
         <v>873</v>
@@ -10193,13 +10205,13 @@
         <v>872</v>
       </c>
       <c r="B239" t="s">
-        <v>1577</v>
+        <v>406</v>
       </c>
       <c r="D239" t="s">
-        <v>1578</v>
+        <v>407</v>
       </c>
       <c r="E239" t="s">
-        <v>1579</v>
+        <v>408</v>
       </c>
       <c r="F239" t="s">
         <v>871</v>
@@ -10213,13 +10225,13 @@
         <v>872</v>
       </c>
       <c r="B240" t="s">
-        <v>409</v>
+        <v>1577</v>
       </c>
       <c r="D240" t="s">
-        <v>410</v>
+        <v>1578</v>
       </c>
       <c r="E240" t="s">
-        <v>411</v>
+        <v>1579</v>
       </c>
       <c r="F240" t="s">
         <v>871</v>
@@ -10233,13 +10245,13 @@
         <v>872</v>
       </c>
       <c r="B241" t="s">
-        <v>928</v>
+        <v>409</v>
       </c>
       <c r="D241" t="s">
-        <v>1117</v>
+        <v>410</v>
       </c>
       <c r="E241" t="s">
-        <v>1179</v>
+        <v>411</v>
       </c>
       <c r="F241" t="s">
         <v>871</v>
@@ -10253,13 +10265,13 @@
         <v>872</v>
       </c>
       <c r="B242" t="s">
-        <v>412</v>
+        <v>928</v>
       </c>
       <c r="D242" t="s">
-        <v>413</v>
+        <v>1117</v>
       </c>
       <c r="E242" t="s">
-        <v>414</v>
+        <v>1179</v>
       </c>
       <c r="F242" t="s">
         <v>871</v>
@@ -10273,13 +10285,13 @@
         <v>872</v>
       </c>
       <c r="B243" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D243" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E243" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F243" t="s">
         <v>871</v>
@@ -10293,13 +10305,13 @@
         <v>872</v>
       </c>
       <c r="B244" t="s">
-        <v>559</v>
+        <v>415</v>
       </c>
       <c r="D244" t="s">
-        <v>1498</v>
+        <v>416</v>
       </c>
       <c r="E244" t="s">
-        <v>560</v>
+        <v>417</v>
       </c>
       <c r="F244" t="s">
         <v>871</v>
@@ -10313,13 +10325,13 @@
         <v>872</v>
       </c>
       <c r="B245" t="s">
-        <v>1272</v>
+        <v>559</v>
       </c>
       <c r="D245" t="s">
-        <v>1273</v>
+        <v>1498</v>
       </c>
       <c r="E245" t="s">
-        <v>1274</v>
+        <v>560</v>
       </c>
       <c r="F245" t="s">
         <v>871</v>
@@ -10333,16 +10345,13 @@
         <v>872</v>
       </c>
       <c r="B246" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C246" t="s">
-        <v>1500</v>
+        <v>1272</v>
       </c>
       <c r="D246" t="s">
-        <v>1501</v>
+        <v>1273</v>
       </c>
       <c r="E246" t="s">
-        <v>1502</v>
+        <v>1274</v>
       </c>
       <c r="F246" t="s">
         <v>871</v>
@@ -10356,13 +10365,16 @@
         <v>872</v>
       </c>
       <c r="B247" t="s">
-        <v>1453</v>
+        <v>1499</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1500</v>
       </c>
       <c r="D247" t="s">
-        <v>1454</v>
+        <v>1501</v>
       </c>
       <c r="E247" t="s">
-        <v>1455</v>
+        <v>1502</v>
       </c>
       <c r="F247" t="s">
         <v>871</v>
@@ -10376,16 +10388,13 @@
         <v>872</v>
       </c>
       <c r="B248" t="s">
-        <v>906</v>
-      </c>
-      <c r="C248" t="s">
-        <v>907</v>
+        <v>1453</v>
       </c>
       <c r="D248" t="s">
-        <v>908</v>
+        <v>1454</v>
       </c>
       <c r="E248" t="s">
-        <v>909</v>
+        <v>1455</v>
       </c>
       <c r="F248" t="s">
         <v>871</v>
@@ -10399,13 +10408,16 @@
         <v>872</v>
       </c>
       <c r="B249" t="s">
-        <v>422</v>
+        <v>906</v>
+      </c>
+      <c r="C249" t="s">
+        <v>907</v>
       </c>
       <c r="D249" t="s">
-        <v>423</v>
+        <v>908</v>
       </c>
       <c r="E249" t="s">
-        <v>424</v>
+        <v>909</v>
       </c>
       <c r="F249" t="s">
         <v>871</v>
@@ -10419,13 +10431,13 @@
         <v>872</v>
       </c>
       <c r="B250" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D250" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E250" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F250" t="s">
         <v>871</v>
@@ -10439,13 +10451,13 @@
         <v>872</v>
       </c>
       <c r="B251" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D251" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E251" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F251" t="s">
         <v>871</v>
@@ -10459,13 +10471,13 @@
         <v>872</v>
       </c>
       <c r="B252" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D252" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E252" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F252" t="s">
         <v>871</v>
@@ -10479,13 +10491,13 @@
         <v>872</v>
       </c>
       <c r="B253" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D253" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E253" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F253" t="s">
         <v>871</v>
@@ -10499,13 +10511,13 @@
         <v>872</v>
       </c>
       <c r="B254" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D254" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E254" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F254" t="s">
         <v>871</v>
@@ -10519,16 +10531,16 @@
         <v>872</v>
       </c>
       <c r="B255" t="s">
-        <v>1021</v>
+        <v>437</v>
       </c>
       <c r="D255" t="s">
-        <v>1022</v>
+        <v>438</v>
       </c>
       <c r="E255" t="s">
-        <v>1275</v>
+        <v>439</v>
       </c>
       <c r="F255" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G255" t="s">
         <v>873</v>
@@ -10539,16 +10551,16 @@
         <v>872</v>
       </c>
       <c r="B256" t="s">
-        <v>440</v>
+        <v>1021</v>
       </c>
       <c r="D256" t="s">
-        <v>441</v>
+        <v>1022</v>
       </c>
       <c r="E256" t="s">
-        <v>442</v>
+        <v>1275</v>
       </c>
       <c r="F256" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G256" t="s">
         <v>873</v>
@@ -10559,13 +10571,13 @@
         <v>872</v>
       </c>
       <c r="B257" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D257" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E257" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F257" t="s">
         <v>871</v>
@@ -10579,13 +10591,13 @@
         <v>872</v>
       </c>
       <c r="B258" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D258" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E258" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F258" t="s">
         <v>871</v>
@@ -10599,13 +10611,13 @@
         <v>872</v>
       </c>
       <c r="B259" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D259" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E259" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F259" t="s">
         <v>871</v>
@@ -10619,19 +10631,16 @@
         <v>872</v>
       </c>
       <c r="B260" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C260" t="s">
-        <v>1024</v>
+        <v>449</v>
       </c>
       <c r="D260" t="s">
-        <v>1025</v>
+        <v>450</v>
       </c>
       <c r="E260" t="s">
-        <v>1276</v>
+        <v>451</v>
       </c>
       <c r="F260" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G260" t="s">
         <v>873</v>
@@ -10642,16 +10651,19 @@
         <v>872</v>
       </c>
       <c r="B261" t="s">
-        <v>452</v>
+        <v>1023</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1024</v>
       </c>
       <c r="D261" t="s">
-        <v>453</v>
+        <v>1025</v>
       </c>
       <c r="E261" t="s">
-        <v>454</v>
+        <v>1276</v>
       </c>
       <c r="F261" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G261" t="s">
         <v>873</v>
@@ -10662,13 +10674,13 @@
         <v>872</v>
       </c>
       <c r="B262" t="s">
-        <v>1277</v>
+        <v>452</v>
       </c>
       <c r="D262" t="s">
-        <v>917</v>
+        <v>453</v>
       </c>
       <c r="E262" t="s">
-        <v>1278</v>
+        <v>454</v>
       </c>
       <c r="F262" t="s">
         <v>871</v>
@@ -10682,13 +10694,13 @@
         <v>872</v>
       </c>
       <c r="B263" t="s">
-        <v>455</v>
+        <v>1277</v>
       </c>
       <c r="D263" t="s">
-        <v>456</v>
+        <v>917</v>
       </c>
       <c r="E263" t="s">
-        <v>457</v>
+        <v>1278</v>
       </c>
       <c r="F263" t="s">
         <v>871</v>
@@ -10702,13 +10714,13 @@
         <v>872</v>
       </c>
       <c r="B264" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D264" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E264" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F264" t="s">
         <v>871</v>
@@ -10722,13 +10734,13 @@
         <v>872</v>
       </c>
       <c r="B265" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D265" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E265" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F265" t="s">
         <v>871</v>
@@ -10742,13 +10754,13 @@
         <v>872</v>
       </c>
       <c r="B266" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D266" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E266" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F266" t="s">
         <v>871</v>
@@ -10762,13 +10774,13 @@
         <v>872</v>
       </c>
       <c r="B267" t="s">
-        <v>1456</v>
+        <v>464</v>
       </c>
       <c r="D267" t="s">
-        <v>1457</v>
+        <v>465</v>
       </c>
       <c r="E267" t="s">
-        <v>1458</v>
+        <v>466</v>
       </c>
       <c r="F267" t="s">
         <v>871</v>
@@ -10782,13 +10794,13 @@
         <v>872</v>
       </c>
       <c r="B268" t="s">
-        <v>467</v>
+        <v>1456</v>
       </c>
       <c r="D268" t="s">
-        <v>468</v>
+        <v>1457</v>
       </c>
       <c r="E268" t="s">
-        <v>469</v>
+        <v>1458</v>
       </c>
       <c r="F268" t="s">
         <v>871</v>
@@ -10802,13 +10814,13 @@
         <v>872</v>
       </c>
       <c r="B269" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D269" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E269" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F269" t="s">
         <v>871</v>
@@ -10822,13 +10834,13 @@
         <v>872</v>
       </c>
       <c r="B270" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D270" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E270" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F270" t="s">
         <v>871</v>
@@ -10842,19 +10854,16 @@
         <v>872</v>
       </c>
       <c r="B271" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C271" t="s">
-        <v>1027</v>
+        <v>473</v>
       </c>
       <c r="D271" t="s">
-        <v>1028</v>
+        <v>474</v>
       </c>
       <c r="E271" t="s">
-        <v>1279</v>
+        <v>475</v>
       </c>
       <c r="F271" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G271" t="s">
         <v>873</v>
@@ -10865,16 +10874,19 @@
         <v>872</v>
       </c>
       <c r="B272" t="s">
-        <v>476</v>
+        <v>1026</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1027</v>
       </c>
       <c r="D272" t="s">
-        <v>477</v>
+        <v>1028</v>
       </c>
       <c r="E272" t="s">
-        <v>478</v>
+        <v>1279</v>
       </c>
       <c r="F272" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G272" t="s">
         <v>873</v>
@@ -10885,13 +10897,13 @@
         <v>872</v>
       </c>
       <c r="B273" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D273" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E273" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F273" t="s">
         <v>871</v>
@@ -10905,13 +10917,13 @@
         <v>872</v>
       </c>
       <c r="B274" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D274" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E274" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F274" t="s">
         <v>871</v>
@@ -10925,16 +10937,16 @@
         <v>872</v>
       </c>
       <c r="B275" t="s">
-        <v>1029</v>
+        <v>482</v>
       </c>
       <c r="D275" t="s">
-        <v>1030</v>
+        <v>483</v>
       </c>
       <c r="E275" t="s">
-        <v>1280</v>
+        <v>484</v>
       </c>
       <c r="F275" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G275" t="s">
         <v>873</v>
@@ -10945,16 +10957,16 @@
         <v>872</v>
       </c>
       <c r="B276" t="s">
-        <v>485</v>
+        <v>1029</v>
       </c>
       <c r="D276" t="s">
-        <v>486</v>
+        <v>1030</v>
       </c>
       <c r="E276" t="s">
-        <v>487</v>
+        <v>1280</v>
       </c>
       <c r="F276" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G276" t="s">
         <v>873</v>
@@ -10965,16 +10977,13 @@
         <v>872</v>
       </c>
       <c r="B277" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C277" t="s">
-        <v>1504</v>
+        <v>485</v>
       </c>
       <c r="D277" t="s">
-        <v>1580</v>
+        <v>486</v>
       </c>
       <c r="E277" t="s">
-        <v>1505</v>
+        <v>487</v>
       </c>
       <c r="F277" t="s">
         <v>871</v>
@@ -10988,16 +10997,19 @@
         <v>872</v>
       </c>
       <c r="B278" t="s">
-        <v>1031</v>
+        <v>1503</v>
+      </c>
+      <c r="C278" t="s">
+        <v>1504</v>
       </c>
       <c r="D278" t="s">
-        <v>1506</v>
+        <v>1580</v>
       </c>
       <c r="E278" t="s">
-        <v>1281</v>
+        <v>1505</v>
       </c>
       <c r="F278" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G278" t="s">
         <v>873</v>
@@ -11008,13 +11020,13 @@
         <v>872</v>
       </c>
       <c r="B279" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D279" t="s">
-        <v>1033</v>
+        <v>1506</v>
       </c>
       <c r="E279" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F279" t="s">
         <v>947</v>
@@ -11028,13 +11040,13 @@
         <v>872</v>
       </c>
       <c r="B280" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D280" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E280" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F280" t="s">
         <v>947</v>
@@ -11048,16 +11060,16 @@
         <v>872</v>
       </c>
       <c r="B281" t="s">
-        <v>488</v>
+        <v>1034</v>
       </c>
       <c r="D281" t="s">
-        <v>489</v>
+        <v>1035</v>
       </c>
       <c r="E281" t="s">
-        <v>490</v>
+        <v>1283</v>
       </c>
       <c r="F281" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G281" t="s">
         <v>873</v>
@@ -11068,13 +11080,13 @@
         <v>872</v>
       </c>
       <c r="B282" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D282" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E282" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F282" t="s">
         <v>871</v>
@@ -11088,13 +11100,13 @@
         <v>872</v>
       </c>
       <c r="B283" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D283" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E283" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F283" t="s">
         <v>871</v>
@@ -11108,13 +11120,13 @@
         <v>872</v>
       </c>
       <c r="B284" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D284" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E284" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F284" t="s">
         <v>871</v>
@@ -11128,13 +11140,13 @@
         <v>872</v>
       </c>
       <c r="B285" t="s">
-        <v>1581</v>
+        <v>497</v>
       </c>
       <c r="D285" t="s">
-        <v>1582</v>
+        <v>498</v>
       </c>
       <c r="E285" t="s">
-        <v>1583</v>
+        <v>499</v>
       </c>
       <c r="F285" t="s">
         <v>871</v>
@@ -11148,13 +11160,13 @@
         <v>872</v>
       </c>
       <c r="B286" t="s">
-        <v>500</v>
+        <v>1581</v>
       </c>
       <c r="D286" t="s">
-        <v>501</v>
+        <v>1582</v>
       </c>
       <c r="E286" t="s">
-        <v>502</v>
+        <v>1583</v>
       </c>
       <c r="F286" t="s">
         <v>871</v>
@@ -11168,16 +11180,16 @@
         <v>872</v>
       </c>
       <c r="B287" t="s">
-        <v>1036</v>
+        <v>500</v>
       </c>
       <c r="D287" t="s">
-        <v>1037</v>
+        <v>501</v>
       </c>
       <c r="E287" t="s">
-        <v>1284</v>
+        <v>502</v>
       </c>
       <c r="F287" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G287" t="s">
         <v>873</v>
@@ -11188,16 +11200,13 @@
         <v>872</v>
       </c>
       <c r="B288" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C288" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="D288" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E288" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F288" t="s">
         <v>947</v>
@@ -11211,16 +11220,19 @@
         <v>872</v>
       </c>
       <c r="B289" t="s">
-        <v>1286</v>
+        <v>1038</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1039</v>
       </c>
       <c r="D289" t="s">
-        <v>1287</v>
+        <v>1040</v>
       </c>
       <c r="E289" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="F289" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G289" t="s">
         <v>873</v>
@@ -11231,13 +11243,13 @@
         <v>872</v>
       </c>
       <c r="B290" t="s">
-        <v>505</v>
+        <v>1286</v>
       </c>
       <c r="D290" t="s">
-        <v>506</v>
+        <v>1287</v>
       </c>
       <c r="E290" t="s">
-        <v>507</v>
+        <v>1288</v>
       </c>
       <c r="F290" t="s">
         <v>871</v>
@@ -11251,13 +11263,13 @@
         <v>872</v>
       </c>
       <c r="B291" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D291" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E291" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F291" t="s">
         <v>871</v>
@@ -11271,19 +11283,16 @@
         <v>872</v>
       </c>
       <c r="B292" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C292" t="s">
-        <v>1042</v>
+        <v>508</v>
       </c>
       <c r="D292" t="s">
-        <v>1043</v>
+        <v>509</v>
       </c>
       <c r="E292" t="s">
-        <v>1289</v>
+        <v>510</v>
       </c>
       <c r="F292" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G292" t="s">
         <v>873</v>
@@ -11294,16 +11303,19 @@
         <v>872</v>
       </c>
       <c r="B293" t="s">
-        <v>511</v>
+        <v>1041</v>
+      </c>
+      <c r="C293" t="s">
+        <v>1042</v>
       </c>
       <c r="D293" t="s">
-        <v>512</v>
+        <v>1043</v>
       </c>
       <c r="E293" t="s">
-        <v>513</v>
+        <v>1289</v>
       </c>
       <c r="F293" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G293" t="s">
         <v>873</v>
@@ -11314,13 +11326,13 @@
         <v>872</v>
       </c>
       <c r="B294" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D294" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E294" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F294" t="s">
         <v>871</v>
@@ -11334,19 +11346,16 @@
         <v>872</v>
       </c>
       <c r="B295" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C295" t="s">
-        <v>1045</v>
+        <v>514</v>
       </c>
       <c r="D295" t="s">
-        <v>1046</v>
+        <v>515</v>
       </c>
       <c r="E295" t="s">
-        <v>1290</v>
+        <v>516</v>
       </c>
       <c r="F295" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G295" t="s">
         <v>873</v>
@@ -11357,16 +11366,19 @@
         <v>872</v>
       </c>
       <c r="B296" t="s">
-        <v>517</v>
+        <v>1044</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1045</v>
       </c>
       <c r="D296" t="s">
-        <v>518</v>
+        <v>1046</v>
       </c>
       <c r="E296" t="s">
-        <v>519</v>
+        <v>1290</v>
       </c>
       <c r="F296" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G296" t="s">
         <v>873</v>
@@ -11377,16 +11389,13 @@
         <v>872</v>
       </c>
       <c r="B297" t="s">
-        <v>867</v>
-      </c>
-      <c r="C297" t="s">
-        <v>868</v>
+        <v>517</v>
       </c>
       <c r="D297" t="s">
-        <v>869</v>
+        <v>518</v>
       </c>
       <c r="E297" t="s">
-        <v>870</v>
+        <v>519</v>
       </c>
       <c r="F297" t="s">
         <v>871</v>
@@ -11400,13 +11409,16 @@
         <v>872</v>
       </c>
       <c r="B298" t="s">
-        <v>1631</v>
+        <v>867</v>
+      </c>
+      <c r="C298" t="s">
+        <v>868</v>
       </c>
       <c r="D298" t="s">
-        <v>1632</v>
+        <v>869</v>
       </c>
       <c r="E298" t="s">
-        <v>1633</v>
+        <v>870</v>
       </c>
       <c r="F298" t="s">
         <v>871</v>
@@ -11420,13 +11432,13 @@
         <v>872</v>
       </c>
       <c r="B299" t="s">
-        <v>520</v>
+        <v>1631</v>
       </c>
       <c r="D299" t="s">
-        <v>521</v>
+        <v>1632</v>
       </c>
       <c r="E299" t="s">
-        <v>522</v>
+        <v>1633</v>
       </c>
       <c r="F299" t="s">
         <v>871</v>
@@ -11440,16 +11452,16 @@
         <v>872</v>
       </c>
       <c r="B300" t="s">
-        <v>1459</v>
+        <v>520</v>
       </c>
       <c r="D300" t="s">
-        <v>1460</v>
+        <v>521</v>
       </c>
       <c r="E300" t="s">
-        <v>1417</v>
+        <v>522</v>
       </c>
       <c r="F300" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G300" t="s">
         <v>873</v>
@@ -11460,16 +11472,16 @@
         <v>872</v>
       </c>
       <c r="B301" t="s">
-        <v>523</v>
+        <v>1459</v>
       </c>
       <c r="D301" t="s">
-        <v>524</v>
+        <v>1460</v>
       </c>
       <c r="E301" t="s">
-        <v>525</v>
+        <v>1417</v>
       </c>
       <c r="F301" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G301" t="s">
         <v>873</v>
@@ -11480,13 +11492,13 @@
         <v>872</v>
       </c>
       <c r="B302" t="s">
-        <v>526</v>
+        <v>1656</v>
       </c>
       <c r="D302" t="s">
-        <v>527</v>
+        <v>1657</v>
       </c>
       <c r="E302" t="s">
-        <v>528</v>
+        <v>1658</v>
       </c>
       <c r="F302" t="s">
         <v>871</v>
@@ -11500,13 +11512,13 @@
         <v>872</v>
       </c>
       <c r="B303" t="s">
-        <v>904</v>
+        <v>523</v>
       </c>
       <c r="D303" t="s">
-        <v>1291</v>
+        <v>524</v>
       </c>
       <c r="E303" t="s">
-        <v>905</v>
+        <v>525</v>
       </c>
       <c r="F303" t="s">
         <v>871</v>
@@ -11520,16 +11532,13 @@
         <v>872</v>
       </c>
       <c r="B304" t="s">
-        <v>898</v>
-      </c>
-      <c r="C304" t="s">
-        <v>899</v>
+        <v>526</v>
       </c>
       <c r="D304" t="s">
-        <v>1292</v>
+        <v>527</v>
       </c>
       <c r="E304" t="s">
-        <v>900</v>
+        <v>528</v>
       </c>
       <c r="F304" t="s">
         <v>871</v>
@@ -11543,13 +11552,13 @@
         <v>872</v>
       </c>
       <c r="B305" t="s">
-        <v>1461</v>
+        <v>904</v>
       </c>
       <c r="D305" t="s">
-        <v>1462</v>
+        <v>1291</v>
       </c>
       <c r="E305" t="s">
-        <v>1463</v>
+        <v>905</v>
       </c>
       <c r="F305" t="s">
         <v>871</v>
@@ -11563,13 +11572,16 @@
         <v>872</v>
       </c>
       <c r="B306" t="s">
-        <v>529</v>
+        <v>898</v>
+      </c>
+      <c r="C306" t="s">
+        <v>899</v>
       </c>
       <c r="D306" t="s">
-        <v>530</v>
+        <v>1292</v>
       </c>
       <c r="E306" t="s">
-        <v>531</v>
+        <v>900</v>
       </c>
       <c r="F306" t="s">
         <v>871</v>
@@ -11583,16 +11595,16 @@
         <v>872</v>
       </c>
       <c r="B307" t="s">
-        <v>1154</v>
+        <v>1461</v>
       </c>
       <c r="D307" t="s">
-        <v>1116</v>
+        <v>1462</v>
       </c>
       <c r="E307" t="s">
-        <v>1155</v>
+        <v>1463</v>
       </c>
       <c r="F307" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G307" t="s">
         <v>873</v>
@@ -11603,13 +11615,13 @@
         <v>872</v>
       </c>
       <c r="B308" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D308" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E308" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F308" t="s">
         <v>871</v>
@@ -11623,16 +11635,16 @@
         <v>872</v>
       </c>
       <c r="B309" t="s">
-        <v>535</v>
+        <v>1154</v>
       </c>
       <c r="D309" t="s">
-        <v>536</v>
+        <v>1116</v>
       </c>
       <c r="E309" t="s">
-        <v>537</v>
+        <v>1155</v>
       </c>
       <c r="F309" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G309" t="s">
         <v>873</v>
@@ -11643,13 +11655,13 @@
         <v>872</v>
       </c>
       <c r="B310" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D310" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E310" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="F310" t="s">
         <v>871</v>
@@ -11663,19 +11675,16 @@
         <v>872</v>
       </c>
       <c r="B311" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C311" t="s">
-        <v>1048</v>
+        <v>535</v>
       </c>
       <c r="D311" t="s">
-        <v>1049</v>
+        <v>536</v>
       </c>
       <c r="E311" t="s">
-        <v>1293</v>
+        <v>537</v>
       </c>
       <c r="F311" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G311" t="s">
         <v>873</v>
@@ -11686,13 +11695,13 @@
         <v>872</v>
       </c>
       <c r="B312" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D312" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E312" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F312" t="s">
         <v>871</v>
@@ -11706,16 +11715,19 @@
         <v>872</v>
       </c>
       <c r="B313" t="s">
-        <v>544</v>
+        <v>1047</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1048</v>
       </c>
       <c r="D313" t="s">
-        <v>545</v>
+        <v>1049</v>
       </c>
       <c r="E313" t="s">
-        <v>546</v>
+        <v>1293</v>
       </c>
       <c r="F313" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G313" t="s">
         <v>873</v>
@@ -11726,13 +11738,13 @@
         <v>872</v>
       </c>
       <c r="B314" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D314" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E314" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="F314" t="s">
         <v>871</v>
@@ -11746,16 +11758,16 @@
         <v>872</v>
       </c>
       <c r="B315" t="s">
-        <v>1507</v>
+        <v>544</v>
       </c>
       <c r="D315" t="s">
-        <v>1508</v>
+        <v>545</v>
       </c>
       <c r="E315" t="s">
-        <v>1509</v>
+        <v>546</v>
       </c>
       <c r="F315" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G315" t="s">
         <v>873</v>
@@ -11766,13 +11778,13 @@
         <v>872</v>
       </c>
       <c r="B316" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D316" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E316" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F316" t="s">
         <v>871</v>
@@ -11786,13 +11798,13 @@
         <v>872</v>
       </c>
       <c r="B317" t="s">
-        <v>1050</v>
+        <v>1507</v>
       </c>
       <c r="D317" t="s">
-        <v>1051</v>
+        <v>1508</v>
       </c>
       <c r="E317" t="s">
-        <v>1294</v>
+        <v>1509</v>
       </c>
       <c r="F317" t="s">
         <v>947</v>
@@ -11806,16 +11818,16 @@
         <v>872</v>
       </c>
       <c r="B318" t="s">
-        <v>1156</v>
+        <v>550</v>
       </c>
       <c r="D318" t="s">
-        <v>1132</v>
+        <v>551</v>
       </c>
       <c r="E318" t="s">
-        <v>1157</v>
+        <v>552</v>
       </c>
       <c r="F318" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G318" t="s">
         <v>873</v>
@@ -11826,16 +11838,16 @@
         <v>872</v>
       </c>
       <c r="B319" t="s">
-        <v>553</v>
+        <v>1050</v>
       </c>
       <c r="D319" t="s">
-        <v>554</v>
+        <v>1051</v>
       </c>
       <c r="E319" t="s">
-        <v>555</v>
+        <v>1294</v>
       </c>
       <c r="F319" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G319" t="s">
         <v>873</v>
@@ -11846,19 +11858,16 @@
         <v>872</v>
       </c>
       <c r="B320" t="s">
-        <v>929</v>
-      </c>
-      <c r="C320" t="s">
-        <v>942</v>
+        <v>1156</v>
       </c>
       <c r="D320" t="s">
-        <v>918</v>
+        <v>1132</v>
       </c>
       <c r="E320" t="s">
-        <v>1295</v>
+        <v>1157</v>
       </c>
       <c r="F320" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G320" t="s">
         <v>873</v>
@@ -11869,13 +11878,13 @@
         <v>872</v>
       </c>
       <c r="B321" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D321" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E321" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F321" t="s">
         <v>871</v>
@@ -11889,19 +11898,19 @@
         <v>872</v>
       </c>
       <c r="B322" t="s">
-        <v>1052</v>
+        <v>929</v>
       </c>
       <c r="C322" t="s">
-        <v>1053</v>
+        <v>942</v>
       </c>
       <c r="D322" t="s">
-        <v>1054</v>
+        <v>918</v>
       </c>
       <c r="E322" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F322" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G322" t="s">
         <v>873</v>
@@ -11912,16 +11921,16 @@
         <v>872</v>
       </c>
       <c r="B323" t="s">
-        <v>1055</v>
+        <v>556</v>
       </c>
       <c r="D323" t="s">
-        <v>1056</v>
+        <v>557</v>
       </c>
       <c r="E323" t="s">
-        <v>1297</v>
+        <v>558</v>
       </c>
       <c r="F323" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G323" t="s">
         <v>873</v>
@@ -11932,16 +11941,19 @@
         <v>872</v>
       </c>
       <c r="B324" t="s">
-        <v>561</v>
+        <v>1052</v>
+      </c>
+      <c r="C324" t="s">
+        <v>1053</v>
       </c>
       <c r="D324" t="s">
-        <v>562</v>
+        <v>1054</v>
       </c>
       <c r="E324" t="s">
-        <v>563</v>
+        <v>1296</v>
       </c>
       <c r="F324" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G324" t="s">
         <v>873</v>
@@ -11952,19 +11964,16 @@
         <v>872</v>
       </c>
       <c r="B325" t="s">
-        <v>930</v>
-      </c>
-      <c r="C325" t="s">
-        <v>943</v>
+        <v>1055</v>
       </c>
       <c r="D325" t="s">
-        <v>919</v>
+        <v>1056</v>
       </c>
       <c r="E325" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F325" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G325" t="s">
         <v>873</v>
@@ -11975,13 +11984,13 @@
         <v>872</v>
       </c>
       <c r="B326" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D326" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E326" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F326" t="s">
         <v>871</v>
@@ -11995,13 +12004,16 @@
         <v>872</v>
       </c>
       <c r="B327" t="s">
-        <v>404</v>
+        <v>930</v>
+      </c>
+      <c r="C327" t="s">
+        <v>943</v>
       </c>
       <c r="D327" t="s">
-        <v>1118</v>
+        <v>919</v>
       </c>
       <c r="E327" t="s">
-        <v>405</v>
+        <v>1298</v>
       </c>
       <c r="F327" t="s">
         <v>871</v>
@@ -12015,13 +12027,13 @@
         <v>872</v>
       </c>
       <c r="B328" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="D328" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E328" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F328" t="s">
         <v>871</v>
@@ -12035,13 +12047,13 @@
         <v>872</v>
       </c>
       <c r="B329" t="s">
-        <v>1299</v>
+        <v>404</v>
       </c>
       <c r="D329" t="s">
-        <v>1300</v>
+        <v>1118</v>
       </c>
       <c r="E329" t="s">
-        <v>1301</v>
+        <v>405</v>
       </c>
       <c r="F329" t="s">
         <v>871</v>
@@ -12055,13 +12067,13 @@
         <v>872</v>
       </c>
       <c r="B330" t="s">
-        <v>1302</v>
+        <v>567</v>
       </c>
       <c r="D330" t="s">
-        <v>1303</v>
+        <v>568</v>
       </c>
       <c r="E330" t="s">
-        <v>1304</v>
+        <v>569</v>
       </c>
       <c r="F330" t="s">
         <v>871</v>
@@ -12075,13 +12087,13 @@
         <v>872</v>
       </c>
       <c r="B331" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="D331" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
       <c r="E331" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="F331" t="s">
         <v>871</v>
@@ -12095,13 +12107,13 @@
         <v>872</v>
       </c>
       <c r="B332" t="s">
-        <v>570</v>
+        <v>1302</v>
       </c>
       <c r="D332" t="s">
-        <v>571</v>
+        <v>1303</v>
       </c>
       <c r="E332" t="s">
-        <v>572</v>
+        <v>1304</v>
       </c>
       <c r="F332" t="s">
         <v>871</v>
@@ -12115,13 +12127,13 @@
         <v>872</v>
       </c>
       <c r="B333" t="s">
-        <v>573</v>
+        <v>1305</v>
       </c>
       <c r="D333" t="s">
-        <v>574</v>
+        <v>1306</v>
       </c>
       <c r="E333" t="s">
-        <v>575</v>
+        <v>1307</v>
       </c>
       <c r="F333" t="s">
         <v>871</v>
@@ -12135,13 +12147,13 @@
         <v>872</v>
       </c>
       <c r="B334" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="D334" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="E334" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F334" t="s">
         <v>871</v>
@@ -12155,16 +12167,16 @@
         <v>872</v>
       </c>
       <c r="B335" t="s">
-        <v>1057</v>
+        <v>573</v>
       </c>
       <c r="D335" t="s">
-        <v>1058</v>
+        <v>574</v>
       </c>
       <c r="E335" t="s">
-        <v>1308</v>
+        <v>575</v>
       </c>
       <c r="F335" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G335" t="s">
         <v>873</v>
@@ -12175,16 +12187,16 @@
         <v>872</v>
       </c>
       <c r="B336" t="s">
-        <v>1634</v>
+        <v>576</v>
       </c>
       <c r="D336" t="s">
-        <v>1635</v>
+        <v>577</v>
       </c>
       <c r="E336" t="s">
-        <v>1636</v>
+        <v>578</v>
       </c>
       <c r="F336" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G336" t="s">
         <v>873</v>
@@ -12195,16 +12207,16 @@
         <v>872</v>
       </c>
       <c r="B337" t="s">
-        <v>579</v>
+        <v>1057</v>
       </c>
       <c r="D337" t="s">
-        <v>580</v>
+        <v>1058</v>
       </c>
       <c r="E337" t="s">
-        <v>581</v>
+        <v>1308</v>
       </c>
       <c r="F337" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G337" t="s">
         <v>873</v>
@@ -12215,16 +12227,16 @@
         <v>872</v>
       </c>
       <c r="B338" t="s">
-        <v>582</v>
+        <v>1634</v>
       </c>
       <c r="D338" t="s">
-        <v>583</v>
+        <v>1635</v>
       </c>
       <c r="E338" t="s">
-        <v>584</v>
+        <v>1636</v>
       </c>
       <c r="F338" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G338" t="s">
         <v>873</v>
@@ -12235,13 +12247,13 @@
         <v>872</v>
       </c>
       <c r="B339" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D339" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="E339" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F339" t="s">
         <v>871</v>
@@ -12255,13 +12267,13 @@
         <v>872</v>
       </c>
       <c r="B340" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D340" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E340" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F340" t="s">
         <v>871</v>
@@ -12275,13 +12287,13 @@
         <v>872</v>
       </c>
       <c r="B341" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D341" t="s">
-        <v>1119</v>
+        <v>586</v>
       </c>
       <c r="E341" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F341" t="s">
         <v>871</v>
@@ -12295,13 +12307,13 @@
         <v>872</v>
       </c>
       <c r="B342" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D342" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E342" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F342" t="s">
         <v>871</v>
@@ -12315,13 +12327,13 @@
         <v>872</v>
       </c>
       <c r="B343" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D343" t="s">
-        <v>597</v>
+        <v>1119</v>
       </c>
       <c r="E343" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="F343" t="s">
         <v>871</v>
@@ -12335,13 +12347,13 @@
         <v>872</v>
       </c>
       <c r="B344" t="s">
-        <v>1309</v>
+        <v>593</v>
       </c>
       <c r="D344" t="s">
-        <v>1310</v>
+        <v>594</v>
       </c>
       <c r="E344" t="s">
-        <v>1311</v>
+        <v>595</v>
       </c>
       <c r="F344" t="s">
         <v>871</v>
@@ -12355,16 +12367,16 @@
         <v>872</v>
       </c>
       <c r="B345" t="s">
-        <v>1312</v>
+        <v>596</v>
       </c>
       <c r="D345" t="s">
-        <v>1313</v>
+        <v>597</v>
       </c>
       <c r="E345" t="s">
-        <v>1314</v>
+        <v>598</v>
       </c>
       <c r="F345" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G345" t="s">
         <v>873</v>
@@ -12375,16 +12387,16 @@
         <v>872</v>
       </c>
       <c r="B346" t="s">
-        <v>1315</v>
+        <v>1309</v>
       </c>
       <c r="D346" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="E346" t="s">
-        <v>1317</v>
+        <v>1311</v>
       </c>
       <c r="F346" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G346" t="s">
         <v>873</v>
@@ -12395,16 +12407,16 @@
         <v>872</v>
       </c>
       <c r="B347" t="s">
-        <v>599</v>
+        <v>1312</v>
       </c>
       <c r="D347" t="s">
-        <v>600</v>
+        <v>1313</v>
       </c>
       <c r="E347" t="s">
-        <v>601</v>
+        <v>1314</v>
       </c>
       <c r="F347" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G347" t="s">
         <v>873</v>
@@ -12415,16 +12427,16 @@
         <v>872</v>
       </c>
       <c r="B348" t="s">
-        <v>602</v>
+        <v>1315</v>
       </c>
       <c r="D348" t="s">
-        <v>603</v>
+        <v>1316</v>
       </c>
       <c r="E348" t="s">
-        <v>604</v>
+        <v>1317</v>
       </c>
       <c r="F348" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G348" t="s">
         <v>873</v>
@@ -12435,13 +12447,13 @@
         <v>872</v>
       </c>
       <c r="B349" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="D349" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="E349" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="F349" t="s">
         <v>871</v>
@@ -12455,13 +12467,13 @@
         <v>872</v>
       </c>
       <c r="B350" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D350" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="E350" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="F350" t="s">
         <v>871</v>
@@ -12475,16 +12487,16 @@
         <v>872</v>
       </c>
       <c r="B351" t="s">
-        <v>1510</v>
+        <v>605</v>
       </c>
       <c r="D351" t="s">
-        <v>1511</v>
+        <v>606</v>
       </c>
       <c r="E351" t="s">
-        <v>1512</v>
+        <v>607</v>
       </c>
       <c r="F351" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G351" t="s">
         <v>873</v>
@@ -12495,13 +12507,13 @@
         <v>872</v>
       </c>
       <c r="B352" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D352" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E352" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F352" t="s">
         <v>871</v>
@@ -12515,16 +12527,16 @@
         <v>872</v>
       </c>
       <c r="B353" t="s">
-        <v>614</v>
+        <v>1510</v>
       </c>
       <c r="D353" t="s">
-        <v>615</v>
+        <v>1511</v>
       </c>
       <c r="E353" t="s">
-        <v>616</v>
+        <v>1512</v>
       </c>
       <c r="F353" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G353" t="s">
         <v>873</v>
@@ -12535,13 +12547,13 @@
         <v>872</v>
       </c>
       <c r="B354" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D354" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="E354" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="F354" t="s">
         <v>871</v>
@@ -12555,16 +12567,13 @@
         <v>872</v>
       </c>
       <c r="B355" t="s">
-        <v>855</v>
-      </c>
-      <c r="C355" t="s">
-        <v>856</v>
+        <v>614</v>
       </c>
       <c r="D355" t="s">
-        <v>857</v>
+        <v>615</v>
       </c>
       <c r="E355" t="s">
-        <v>858</v>
+        <v>616</v>
       </c>
       <c r="F355" t="s">
         <v>871</v>
@@ -12578,16 +12587,13 @@
         <v>872</v>
       </c>
       <c r="B356" t="s">
-        <v>910</v>
-      </c>
-      <c r="C356" t="s">
-        <v>911</v>
+        <v>617</v>
       </c>
       <c r="D356" t="s">
-        <v>912</v>
+        <v>618</v>
       </c>
       <c r="E356" t="s">
-        <v>913</v>
+        <v>619</v>
       </c>
       <c r="F356" t="s">
         <v>871</v>
@@ -12601,16 +12607,19 @@
         <v>872</v>
       </c>
       <c r="B357" t="s">
-        <v>1110</v>
+        <v>855</v>
+      </c>
+      <c r="C357" t="s">
+        <v>856</v>
       </c>
       <c r="D357" t="s">
-        <v>1111</v>
+        <v>857</v>
       </c>
       <c r="E357" t="s">
-        <v>1318</v>
+        <v>858</v>
       </c>
       <c r="F357" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G357" t="s">
         <v>873</v>
@@ -12621,13 +12630,16 @@
         <v>872</v>
       </c>
       <c r="B358" t="s">
-        <v>620</v>
+        <v>910</v>
+      </c>
+      <c r="C358" t="s">
+        <v>911</v>
       </c>
       <c r="D358" t="s">
-        <v>621</v>
+        <v>912</v>
       </c>
       <c r="E358" t="s">
-        <v>622</v>
+        <v>913</v>
       </c>
       <c r="F358" t="s">
         <v>871</v>
@@ -12641,16 +12653,16 @@
         <v>872</v>
       </c>
       <c r="B359" t="s">
-        <v>1319</v>
+        <v>1110</v>
       </c>
       <c r="D359" t="s">
-        <v>1320</v>
+        <v>1111</v>
       </c>
       <c r="E359" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="F359" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G359" t="s">
         <v>873</v>
@@ -12661,13 +12673,13 @@
         <v>872</v>
       </c>
       <c r="B360" t="s">
-        <v>1322</v>
+        <v>620</v>
       </c>
       <c r="D360" t="s">
-        <v>1323</v>
+        <v>621</v>
       </c>
       <c r="E360" t="s">
-        <v>1324</v>
+        <v>622</v>
       </c>
       <c r="F360" t="s">
         <v>871</v>
@@ -12681,13 +12693,13 @@
         <v>872</v>
       </c>
       <c r="B361" t="s">
-        <v>623</v>
+        <v>1319</v>
       </c>
       <c r="D361" t="s">
-        <v>624</v>
+        <v>1320</v>
       </c>
       <c r="E361" t="s">
-        <v>625</v>
+        <v>1321</v>
       </c>
       <c r="F361" t="s">
         <v>871</v>
@@ -12701,13 +12713,13 @@
         <v>872</v>
       </c>
       <c r="B362" t="s">
-        <v>626</v>
+        <v>1322</v>
       </c>
       <c r="D362" t="s">
-        <v>627</v>
+        <v>1323</v>
       </c>
       <c r="E362" t="s">
-        <v>628</v>
+        <v>1324</v>
       </c>
       <c r="F362" t="s">
         <v>871</v>
@@ -12721,13 +12733,13 @@
         <v>872</v>
       </c>
       <c r="B363" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D363" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="E363" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="F363" t="s">
         <v>871</v>
@@ -12741,13 +12753,13 @@
         <v>872</v>
       </c>
       <c r="B364" t="s">
-        <v>1637</v>
+        <v>626</v>
       </c>
       <c r="D364" t="s">
-        <v>1638</v>
+        <v>627</v>
       </c>
       <c r="E364" t="s">
-        <v>1639</v>
+        <v>628</v>
       </c>
       <c r="F364" t="s">
         <v>871</v>
@@ -12761,13 +12773,13 @@
         <v>872</v>
       </c>
       <c r="B365" t="s">
-        <v>814</v>
+        <v>629</v>
       </c>
       <c r="D365" t="s">
-        <v>1464</v>
+        <v>630</v>
       </c>
       <c r="E365" t="s">
-        <v>815</v>
+        <v>631</v>
       </c>
       <c r="F365" t="s">
         <v>871</v>
@@ -12781,13 +12793,13 @@
         <v>872</v>
       </c>
       <c r="B366" t="s">
-        <v>1584</v>
+        <v>814</v>
       </c>
       <c r="D366" t="s">
-        <v>1585</v>
+        <v>1464</v>
       </c>
       <c r="E366" t="s">
-        <v>1586</v>
+        <v>815</v>
       </c>
       <c r="F366" t="s">
         <v>871</v>
@@ -12801,13 +12813,13 @@
         <v>872</v>
       </c>
       <c r="B367" t="s">
-        <v>934</v>
+        <v>1584</v>
       </c>
       <c r="D367" t="s">
-        <v>924</v>
+        <v>1585</v>
       </c>
       <c r="E367" t="s">
-        <v>1325</v>
+        <v>1586</v>
       </c>
       <c r="F367" t="s">
         <v>871</v>
@@ -12821,13 +12833,13 @@
         <v>872</v>
       </c>
       <c r="B368" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D368" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E368" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="F368" t="s">
         <v>871</v>
@@ -12841,16 +12853,16 @@
         <v>872</v>
       </c>
       <c r="B369" t="s">
-        <v>1158</v>
+        <v>935</v>
       </c>
       <c r="D369" t="s">
-        <v>1120</v>
+        <v>925</v>
       </c>
       <c r="E369" t="s">
-        <v>1159</v>
+        <v>1326</v>
       </c>
       <c r="F369" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G369" t="s">
         <v>873</v>
@@ -12861,16 +12873,16 @@
         <v>872</v>
       </c>
       <c r="B370" t="s">
-        <v>931</v>
+        <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E370" t="s">
-        <v>1180</v>
+        <v>1159</v>
       </c>
       <c r="F370" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G370" t="s">
         <v>873</v>
@@ -12881,13 +12893,13 @@
         <v>872</v>
       </c>
       <c r="B371" t="s">
-        <v>1640</v>
+        <v>931</v>
       </c>
       <c r="D371" t="s">
-        <v>1641</v>
+        <v>1121</v>
       </c>
       <c r="E371" t="s">
-        <v>1642</v>
+        <v>1180</v>
       </c>
       <c r="F371" t="s">
         <v>871</v>
@@ -12901,16 +12913,16 @@
         <v>872</v>
       </c>
       <c r="B372" t="s">
-        <v>634</v>
+        <v>1637</v>
       </c>
       <c r="D372" t="s">
-        <v>635</v>
+        <v>1638</v>
       </c>
       <c r="E372" t="s">
-        <v>636</v>
+        <v>1639</v>
       </c>
       <c r="F372" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G372" t="s">
         <v>873</v>
@@ -12921,16 +12933,16 @@
         <v>872</v>
       </c>
       <c r="B373" t="s">
-        <v>637</v>
+        <v>1640</v>
       </c>
       <c r="D373" t="s">
-        <v>638</v>
+        <v>1641</v>
       </c>
       <c r="E373" t="s">
-        <v>639</v>
+        <v>1642</v>
       </c>
       <c r="F373" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G373" t="s">
         <v>873</v>
@@ -12941,16 +12953,16 @@
         <v>872</v>
       </c>
       <c r="B374" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D374" t="s">
-        <v>1327</v>
+        <v>635</v>
       </c>
       <c r="E374" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="F374" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G374" t="s">
         <v>873</v>
@@ -12961,16 +12973,16 @@
         <v>872</v>
       </c>
       <c r="B375" t="s">
-        <v>1328</v>
+        <v>637</v>
       </c>
       <c r="D375" t="s">
-        <v>1329</v>
+        <v>638</v>
       </c>
       <c r="E375" t="s">
-        <v>1330</v>
+        <v>639</v>
       </c>
       <c r="F375" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G375" t="s">
         <v>873</v>
@@ -12981,16 +12993,13 @@
         <v>872</v>
       </c>
       <c r="B376" t="s">
-        <v>863</v>
-      </c>
-      <c r="C376" t="s">
-        <v>864</v>
+        <v>640</v>
       </c>
       <c r="D376" t="s">
-        <v>865</v>
+        <v>1327</v>
       </c>
       <c r="E376" t="s">
-        <v>866</v>
+        <v>641</v>
       </c>
       <c r="F376" t="s">
         <v>871</v>
@@ -13004,13 +13013,13 @@
         <v>872</v>
       </c>
       <c r="B377" t="s">
-        <v>644</v>
+        <v>1328</v>
       </c>
       <c r="D377" t="s">
-        <v>645</v>
+        <v>1329</v>
       </c>
       <c r="E377" t="s">
-        <v>646</v>
+        <v>1330</v>
       </c>
       <c r="F377" t="s">
         <v>871</v>
@@ -13024,16 +13033,19 @@
         <v>872</v>
       </c>
       <c r="B378" t="s">
-        <v>1059</v>
+        <v>863</v>
+      </c>
+      <c r="C378" t="s">
+        <v>864</v>
       </c>
       <c r="D378" t="s">
-        <v>1060</v>
+        <v>865</v>
       </c>
       <c r="E378" t="s">
-        <v>1331</v>
+        <v>866</v>
       </c>
       <c r="F378" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G378" t="s">
         <v>873</v>
@@ -13044,16 +13056,16 @@
         <v>872</v>
       </c>
       <c r="B379" t="s">
-        <v>1061</v>
+        <v>644</v>
       </c>
       <c r="D379" t="s">
-        <v>1062</v>
+        <v>645</v>
       </c>
       <c r="E379" t="s">
-        <v>1332</v>
+        <v>646</v>
       </c>
       <c r="F379" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G379" t="s">
         <v>873</v>
@@ -13064,13 +13076,13 @@
         <v>872</v>
       </c>
       <c r="B380" t="s">
-        <v>1465</v>
+        <v>1059</v>
       </c>
       <c r="D380" t="s">
-        <v>1466</v>
+        <v>1060</v>
       </c>
       <c r="E380" t="s">
-        <v>1467</v>
+        <v>1331</v>
       </c>
       <c r="F380" t="s">
         <v>947</v>
@@ -13084,16 +13096,13 @@
         <v>872</v>
       </c>
       <c r="B381" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D381" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E381" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F381" t="s">
         <v>947</v>
@@ -13107,16 +13116,16 @@
         <v>872</v>
       </c>
       <c r="B382" t="s">
-        <v>647</v>
+        <v>1465</v>
       </c>
       <c r="D382" t="s">
-        <v>648</v>
+        <v>1466</v>
       </c>
       <c r="E382" t="s">
-        <v>649</v>
+        <v>1467</v>
       </c>
       <c r="F382" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G382" t="s">
         <v>873</v>
@@ -13127,16 +13136,19 @@
         <v>872</v>
       </c>
       <c r="B383" t="s">
-        <v>650</v>
+        <v>1063</v>
+      </c>
+      <c r="C383" t="s">
+        <v>1064</v>
       </c>
       <c r="D383" t="s">
-        <v>651</v>
+        <v>1065</v>
       </c>
       <c r="E383" t="s">
-        <v>652</v>
+        <v>1333</v>
       </c>
       <c r="F383" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G383" t="s">
         <v>873</v>
@@ -13147,16 +13159,16 @@
         <v>872</v>
       </c>
       <c r="B384" t="s">
-        <v>1066</v>
+        <v>647</v>
       </c>
       <c r="D384" t="s">
-        <v>1067</v>
+        <v>648</v>
       </c>
       <c r="E384" t="s">
-        <v>1334</v>
+        <v>649</v>
       </c>
       <c r="F384" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G384" t="s">
         <v>873</v>
@@ -13167,16 +13179,16 @@
         <v>872</v>
       </c>
       <c r="B385" t="s">
-        <v>1643</v>
+        <v>650</v>
       </c>
       <c r="D385" t="s">
-        <v>1644</v>
+        <v>651</v>
       </c>
       <c r="E385" t="s">
-        <v>1645</v>
+        <v>652</v>
       </c>
       <c r="F385" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G385" t="s">
         <v>873</v>
@@ -13187,16 +13199,16 @@
         <v>872</v>
       </c>
       <c r="B386" t="s">
-        <v>653</v>
+        <v>1066</v>
       </c>
       <c r="D386" t="s">
-        <v>654</v>
+        <v>1067</v>
       </c>
       <c r="E386" t="s">
-        <v>655</v>
+        <v>1334</v>
       </c>
       <c r="F386" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G386" t="s">
         <v>873</v>
@@ -13207,13 +13219,13 @@
         <v>872</v>
       </c>
       <c r="B387" t="s">
-        <v>1068</v>
+        <v>1643</v>
       </c>
       <c r="D387" t="s">
-        <v>1069</v>
+        <v>1644</v>
       </c>
       <c r="E387" t="s">
-        <v>1335</v>
+        <v>1645</v>
       </c>
       <c r="F387" t="s">
         <v>947</v>
@@ -13227,13 +13239,13 @@
         <v>872</v>
       </c>
       <c r="B388" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D388" t="s">
-        <v>1513</v>
+        <v>654</v>
       </c>
       <c r="E388" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F388" t="s">
         <v>871</v>
@@ -13247,19 +13259,16 @@
         <v>872</v>
       </c>
       <c r="B389" t="s">
-        <v>1514</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1515</v>
+        <v>1068</v>
       </c>
       <c r="D389" t="s">
-        <v>1516</v>
+        <v>1069</v>
       </c>
       <c r="E389" t="s">
-        <v>1517</v>
+        <v>1335</v>
       </c>
       <c r="F389" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G389" t="s">
         <v>873</v>
@@ -13270,16 +13279,13 @@
         <v>872</v>
       </c>
       <c r="B390" t="s">
-        <v>1518</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1519</v>
+        <v>656</v>
       </c>
       <c r="D390" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="E390" t="s">
-        <v>1521</v>
+        <v>657</v>
       </c>
       <c r="F390" t="s">
         <v>871</v>
@@ -13293,13 +13299,16 @@
         <v>872</v>
       </c>
       <c r="B391" t="s">
-        <v>658</v>
+        <v>1514</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1515</v>
       </c>
       <c r="D391" t="s">
-        <v>659</v>
+        <v>1516</v>
       </c>
       <c r="E391" t="s">
-        <v>660</v>
+        <v>1517</v>
       </c>
       <c r="F391" t="s">
         <v>871</v>
@@ -13313,19 +13322,19 @@
         <v>872</v>
       </c>
       <c r="B392" t="s">
-        <v>1070</v>
+        <v>1518</v>
       </c>
       <c r="C392" t="s">
-        <v>1071</v>
+        <v>1519</v>
       </c>
       <c r="D392" t="s">
-        <v>1072</v>
+        <v>1520</v>
       </c>
       <c r="E392" t="s">
-        <v>1336</v>
+        <v>1521</v>
       </c>
       <c r="F392" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G392" t="s">
         <v>873</v>
@@ -13336,13 +13345,13 @@
         <v>872</v>
       </c>
       <c r="B393" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D393" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E393" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F393" t="s">
         <v>871</v>
@@ -13356,19 +13365,22 @@
         <v>872</v>
       </c>
       <c r="B394" t="s">
-        <v>1560</v>
+        <v>1070</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1071</v>
       </c>
       <c r="D394" t="s">
-        <v>1561</v>
+        <v>1072</v>
       </c>
       <c r="E394" t="s">
-        <v>1562</v>
+        <v>1336</v>
       </c>
       <c r="F394" t="s">
         <v>947</v>
       </c>
       <c r="G394" t="s">
-        <v>1556</v>
+        <v>873</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -13376,13 +13388,13 @@
         <v>872</v>
       </c>
       <c r="B395" t="s">
-        <v>1337</v>
+        <v>661</v>
       </c>
       <c r="D395" t="s">
-        <v>1338</v>
+        <v>662</v>
       </c>
       <c r="E395" t="s">
-        <v>1339</v>
+        <v>663</v>
       </c>
       <c r="F395" t="s">
         <v>871</v>
@@ -13396,19 +13408,19 @@
         <v>872</v>
       </c>
       <c r="B396" t="s">
-        <v>1073</v>
+        <v>1560</v>
       </c>
       <c r="D396" t="s">
-        <v>1074</v>
+        <v>1561</v>
       </c>
       <c r="E396" t="s">
-        <v>1340</v>
+        <v>1562</v>
       </c>
       <c r="F396" t="s">
         <v>947</v>
       </c>
       <c r="G396" t="s">
-        <v>873</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -13416,13 +13428,13 @@
         <v>872</v>
       </c>
       <c r="B397" t="s">
-        <v>167</v>
+        <v>1337</v>
       </c>
       <c r="D397" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="E397" t="s">
-        <v>168</v>
+        <v>1339</v>
       </c>
       <c r="F397" t="s">
         <v>871</v>
@@ -13436,16 +13448,16 @@
         <v>872</v>
       </c>
       <c r="B398" t="s">
-        <v>68</v>
+        <v>1073</v>
       </c>
       <c r="D398" t="s">
-        <v>1342</v>
+        <v>1074</v>
       </c>
       <c r="E398" t="s">
-        <v>69</v>
+        <v>1340</v>
       </c>
       <c r="F398" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G398" t="s">
         <v>873</v>
@@ -13456,16 +13468,13 @@
         <v>872</v>
       </c>
       <c r="B399" t="s">
-        <v>932</v>
-      </c>
-      <c r="C399" t="s">
-        <v>944</v>
+        <v>167</v>
       </c>
       <c r="D399" t="s">
-        <v>920</v>
+        <v>1341</v>
       </c>
       <c r="E399" t="s">
-        <v>1343</v>
+        <v>168</v>
       </c>
       <c r="F399" t="s">
         <v>871</v>
@@ -13479,13 +13488,13 @@
         <v>872</v>
       </c>
       <c r="B400" t="s">
-        <v>666</v>
+        <v>68</v>
       </c>
       <c r="D400" t="s">
-        <v>667</v>
+        <v>1342</v>
       </c>
       <c r="E400" t="s">
-        <v>668</v>
+        <v>69</v>
       </c>
       <c r="F400" t="s">
         <v>871</v>
@@ -13499,13 +13508,16 @@
         <v>872</v>
       </c>
       <c r="B401" t="s">
-        <v>669</v>
+        <v>932</v>
+      </c>
+      <c r="C401" t="s">
+        <v>944</v>
       </c>
       <c r="D401" t="s">
-        <v>670</v>
+        <v>920</v>
       </c>
       <c r="E401" t="s">
-        <v>671</v>
+        <v>1343</v>
       </c>
       <c r="F401" t="s">
         <v>871</v>
@@ -13519,13 +13531,13 @@
         <v>872</v>
       </c>
       <c r="B402" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D402" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="E402" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F402" t="s">
         <v>871</v>
@@ -13539,16 +13551,16 @@
         <v>872</v>
       </c>
       <c r="B403" t="s">
-        <v>1075</v>
+        <v>669</v>
       </c>
       <c r="D403" t="s">
-        <v>1076</v>
+        <v>670</v>
       </c>
       <c r="E403" t="s">
-        <v>1344</v>
+        <v>671</v>
       </c>
       <c r="F403" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G403" t="s">
         <v>873</v>
@@ -13559,16 +13571,16 @@
         <v>872</v>
       </c>
       <c r="B404" t="s">
-        <v>1077</v>
+        <v>672</v>
       </c>
       <c r="D404" t="s">
-        <v>1078</v>
+        <v>673</v>
       </c>
       <c r="E404" t="s">
-        <v>1345</v>
+        <v>674</v>
       </c>
       <c r="F404" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G404" t="s">
         <v>873</v>
@@ -13579,13 +13591,13 @@
         <v>872</v>
       </c>
       <c r="B405" t="s">
-        <v>1346</v>
+        <v>1075</v>
       </c>
       <c r="D405" t="s">
-        <v>1347</v>
+        <v>1076</v>
       </c>
       <c r="E405" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="F405" t="s">
         <v>947</v>
@@ -13599,13 +13611,13 @@
         <v>872</v>
       </c>
       <c r="B406" t="s">
-        <v>1160</v>
+        <v>1077</v>
       </c>
       <c r="D406" t="s">
-        <v>1126</v>
+        <v>1078</v>
       </c>
       <c r="E406" t="s">
-        <v>1161</v>
+        <v>1345</v>
       </c>
       <c r="F406" t="s">
         <v>947</v>
@@ -13619,13 +13631,13 @@
         <v>872</v>
       </c>
       <c r="B407" t="s">
-        <v>1079</v>
+        <v>1346</v>
       </c>
       <c r="D407" t="s">
-        <v>1080</v>
+        <v>1347</v>
       </c>
       <c r="E407" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F407" t="s">
         <v>947</v>
@@ -13639,13 +13651,13 @@
         <v>872</v>
       </c>
       <c r="B408" t="s">
-        <v>1081</v>
+        <v>1160</v>
       </c>
       <c r="D408" t="s">
-        <v>1082</v>
+        <v>1126</v>
       </c>
       <c r="E408" t="s">
-        <v>1350</v>
+        <v>1161</v>
       </c>
       <c r="F408" t="s">
         <v>947</v>
@@ -13659,13 +13671,13 @@
         <v>872</v>
       </c>
       <c r="B409" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D409" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E409" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="F409" t="s">
         <v>947</v>
@@ -13679,13 +13691,13 @@
         <v>872</v>
       </c>
       <c r="B410" t="s">
-        <v>1162</v>
+        <v>1081</v>
       </c>
       <c r="D410" t="s">
-        <v>1133</v>
+        <v>1082</v>
       </c>
       <c r="E410" t="s">
-        <v>1163</v>
+        <v>1350</v>
       </c>
       <c r="F410" t="s">
         <v>947</v>
@@ -13699,16 +13711,16 @@
         <v>872</v>
       </c>
       <c r="B411" t="s">
-        <v>675</v>
+        <v>1083</v>
       </c>
       <c r="D411" t="s">
-        <v>676</v>
+        <v>1084</v>
       </c>
       <c r="E411" t="s">
-        <v>677</v>
+        <v>1351</v>
       </c>
       <c r="F411" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G411" t="s">
         <v>873</v>
@@ -13719,16 +13731,16 @@
         <v>872</v>
       </c>
       <c r="B412" t="s">
-        <v>678</v>
+        <v>1162</v>
       </c>
       <c r="D412" t="s">
-        <v>679</v>
+        <v>1133</v>
       </c>
       <c r="E412" t="s">
-        <v>680</v>
+        <v>1163</v>
       </c>
       <c r="F412" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G412" t="s">
         <v>873</v>
@@ -13739,16 +13751,13 @@
         <v>872</v>
       </c>
       <c r="B413" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C413" t="s">
-        <v>945</v>
+        <v>675</v>
       </c>
       <c r="D413" t="s">
-        <v>1353</v>
+        <v>676</v>
       </c>
       <c r="E413" t="s">
-        <v>1354</v>
+        <v>677</v>
       </c>
       <c r="F413" t="s">
         <v>871</v>
@@ -13762,13 +13771,13 @@
         <v>872</v>
       </c>
       <c r="B414" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D414" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E414" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F414" t="s">
         <v>871</v>
@@ -13782,13 +13791,16 @@
         <v>872</v>
       </c>
       <c r="B415" t="s">
-        <v>684</v>
+        <v>1352</v>
+      </c>
+      <c r="C415" t="s">
+        <v>945</v>
       </c>
       <c r="D415" t="s">
-        <v>685</v>
+        <v>1353</v>
       </c>
       <c r="E415" t="s">
-        <v>686</v>
+        <v>1354</v>
       </c>
       <c r="F415" t="s">
         <v>871</v>
@@ -13802,16 +13814,16 @@
         <v>872</v>
       </c>
       <c r="B416" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D416" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="E416" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="F416" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G416" t="s">
         <v>873</v>
@@ -13822,13 +13834,13 @@
         <v>872</v>
       </c>
       <c r="B417" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D417" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E417" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="F417" t="s">
         <v>871</v>
@@ -13842,16 +13854,16 @@
         <v>872</v>
       </c>
       <c r="B418" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D418" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E418" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="F418" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G418" t="s">
         <v>873</v>
@@ -13862,13 +13874,13 @@
         <v>872</v>
       </c>
       <c r="B419" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D419" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E419" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F419" t="s">
         <v>871</v>
@@ -13882,13 +13894,13 @@
         <v>872</v>
       </c>
       <c r="B420" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="D420" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E420" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="F420" t="s">
         <v>871</v>
@@ -13902,16 +13914,13 @@
         <v>872</v>
       </c>
       <c r="B421" t="s">
-        <v>894</v>
-      </c>
-      <c r="C421" t="s">
-        <v>895</v>
+        <v>698</v>
       </c>
       <c r="D421" t="s">
-        <v>896</v>
+        <v>699</v>
       </c>
       <c r="E421" t="s">
-        <v>897</v>
+        <v>700</v>
       </c>
       <c r="F421" t="s">
         <v>871</v>
@@ -13925,13 +13934,13 @@
         <v>872</v>
       </c>
       <c r="B422" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D422" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E422" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F422" t="s">
         <v>871</v>
@@ -13945,16 +13954,19 @@
         <v>872</v>
       </c>
       <c r="B423" t="s">
-        <v>1164</v>
+        <v>894</v>
+      </c>
+      <c r="C423" t="s">
+        <v>895</v>
       </c>
       <c r="D423" t="s">
-        <v>1134</v>
+        <v>896</v>
       </c>
       <c r="E423" t="s">
-        <v>1165</v>
+        <v>897</v>
       </c>
       <c r="F423" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G423" t="s">
         <v>873</v>
@@ -13965,13 +13977,13 @@
         <v>872</v>
       </c>
       <c r="B424" t="s">
-        <v>1355</v>
+        <v>704</v>
       </c>
       <c r="D424" t="s">
-        <v>1356</v>
+        <v>705</v>
       </c>
       <c r="E424" t="s">
-        <v>1357</v>
+        <v>706</v>
       </c>
       <c r="F424" t="s">
         <v>871</v>
@@ -13985,16 +13997,16 @@
         <v>872</v>
       </c>
       <c r="B425" t="s">
-        <v>1358</v>
+        <v>1164</v>
       </c>
       <c r="D425" t="s">
-        <v>1359</v>
+        <v>1134</v>
       </c>
       <c r="E425" t="s">
-        <v>1360</v>
+        <v>1165</v>
       </c>
       <c r="F425" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G425" t="s">
         <v>873</v>
@@ -14005,19 +14017,16 @@
         <v>872</v>
       </c>
       <c r="B426" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C426" t="s">
-        <v>1086</v>
+        <v>1355</v>
       </c>
       <c r="D426" t="s">
-        <v>1087</v>
+        <v>1356</v>
       </c>
       <c r="E426" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="F426" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G426" t="s">
         <v>873</v>
@@ -14028,13 +14037,13 @@
         <v>872</v>
       </c>
       <c r="B427" t="s">
-        <v>707</v>
+        <v>1358</v>
       </c>
       <c r="D427" t="s">
-        <v>708</v>
+        <v>1359</v>
       </c>
       <c r="E427" t="s">
-        <v>709</v>
+        <v>1360</v>
       </c>
       <c r="F427" t="s">
         <v>871</v>
@@ -14048,13 +14057,16 @@
         <v>872</v>
       </c>
       <c r="B428" t="s">
-        <v>1166</v>
+        <v>1085</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1086</v>
       </c>
       <c r="D428" t="s">
-        <v>1167</v>
+        <v>1087</v>
       </c>
       <c r="E428" t="s">
-        <v>1168</v>
+        <v>1361</v>
       </c>
       <c r="F428" t="s">
         <v>947</v>
@@ -14068,16 +14080,16 @@
         <v>872</v>
       </c>
       <c r="B429" t="s">
-        <v>1362</v>
+        <v>707</v>
       </c>
       <c r="D429" t="s">
-        <v>1522</v>
+        <v>708</v>
       </c>
       <c r="E429" t="s">
-        <v>1363</v>
+        <v>709</v>
       </c>
       <c r="F429" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G429" t="s">
         <v>873</v>
@@ -14088,16 +14100,16 @@
         <v>872</v>
       </c>
       <c r="B430" t="s">
-        <v>710</v>
+        <v>1166</v>
       </c>
       <c r="D430" t="s">
-        <v>711</v>
+        <v>1167</v>
       </c>
       <c r="E430" t="s">
-        <v>712</v>
+        <v>1168</v>
       </c>
       <c r="F430" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G430" t="s">
         <v>873</v>
@@ -14108,13 +14120,13 @@
         <v>872</v>
       </c>
       <c r="B431" t="s">
-        <v>1169</v>
+        <v>1362</v>
       </c>
       <c r="D431" t="s">
-        <v>1122</v>
+        <v>1522</v>
       </c>
       <c r="E431" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="F431" t="s">
         <v>947</v>
@@ -14128,13 +14140,13 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D432" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E432" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F432" t="s">
         <v>871</v>
@@ -14148,16 +14160,16 @@
         <v>872</v>
       </c>
       <c r="B433" t="s">
-        <v>716</v>
+        <v>1169</v>
       </c>
       <c r="D433" t="s">
-        <v>717</v>
+        <v>1122</v>
       </c>
       <c r="E433" t="s">
-        <v>718</v>
+        <v>1364</v>
       </c>
       <c r="F433" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G433" t="s">
         <v>873</v>
@@ -14168,13 +14180,13 @@
         <v>872</v>
       </c>
       <c r="B434" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D434" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E434" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F434" t="s">
         <v>871</v>
@@ -14188,13 +14200,13 @@
         <v>872</v>
       </c>
       <c r="B435" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D435" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E435" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F435" t="s">
         <v>871</v>
@@ -14208,13 +14220,13 @@
         <v>872</v>
       </c>
       <c r="B436" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D436" t="s">
-        <v>1587</v>
+        <v>720</v>
       </c>
       <c r="E436" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="F436" t="s">
         <v>871</v>
@@ -14228,16 +14240,16 @@
         <v>872</v>
       </c>
       <c r="B437" t="s">
-        <v>1170</v>
+        <v>722</v>
       </c>
       <c r="D437" t="s">
-        <v>1123</v>
+        <v>723</v>
       </c>
       <c r="E437" t="s">
-        <v>1171</v>
+        <v>724</v>
       </c>
       <c r="F437" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G437" t="s">
         <v>873</v>
@@ -14248,13 +14260,13 @@
         <v>872</v>
       </c>
       <c r="B438" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D438" t="s">
-        <v>728</v>
+        <v>1587</v>
       </c>
       <c r="E438" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F438" t="s">
         <v>871</v>
@@ -14268,16 +14280,16 @@
         <v>872</v>
       </c>
       <c r="B439" t="s">
-        <v>732</v>
+        <v>1170</v>
       </c>
       <c r="D439" t="s">
-        <v>733</v>
+        <v>1123</v>
       </c>
       <c r="E439" t="s">
-        <v>734</v>
+        <v>1171</v>
       </c>
       <c r="F439" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G439" t="s">
         <v>873</v>
@@ -14288,13 +14300,13 @@
         <v>872</v>
       </c>
       <c r="B440" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="D440" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="E440" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="F440" t="s">
         <v>871</v>
@@ -14308,16 +14320,16 @@
         <v>872</v>
       </c>
       <c r="B441" t="s">
-        <v>1468</v>
+        <v>732</v>
       </c>
       <c r="D441" t="s">
-        <v>1469</v>
+        <v>733</v>
       </c>
       <c r="E441" t="s">
-        <v>1470</v>
+        <v>734</v>
       </c>
       <c r="F441" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G441" t="s">
         <v>873</v>
@@ -14328,16 +14340,16 @@
         <v>872</v>
       </c>
       <c r="B442" t="s">
-        <v>1172</v>
+        <v>735</v>
       </c>
       <c r="D442" t="s">
-        <v>1135</v>
+        <v>736</v>
       </c>
       <c r="E442" t="s">
-        <v>1173</v>
+        <v>737</v>
       </c>
       <c r="F442" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G442" t="s">
         <v>873</v>
@@ -14348,16 +14360,16 @@
         <v>872</v>
       </c>
       <c r="B443" t="s">
-        <v>738</v>
+        <v>1468</v>
       </c>
       <c r="D443" t="s">
-        <v>739</v>
+        <v>1469</v>
       </c>
       <c r="E443" t="s">
-        <v>740</v>
+        <v>1470</v>
       </c>
       <c r="F443" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G443" t="s">
         <v>873</v>
@@ -14368,16 +14380,13 @@
         <v>872</v>
       </c>
       <c r="B444" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C444" t="s">
-        <v>1089</v>
+        <v>1172</v>
       </c>
       <c r="D444" t="s">
-        <v>1090</v>
+        <v>1135</v>
       </c>
       <c r="E444" t="s">
-        <v>1365</v>
+        <v>1173</v>
       </c>
       <c r="F444" t="s">
         <v>947</v>
@@ -14391,13 +14400,13 @@
         <v>872</v>
       </c>
       <c r="B445" t="s">
-        <v>1646</v>
+        <v>738</v>
       </c>
       <c r="D445" t="s">
-        <v>1647</v>
+        <v>739</v>
       </c>
       <c r="E445" t="s">
-        <v>1648</v>
+        <v>740</v>
       </c>
       <c r="F445" t="s">
         <v>871</v>
@@ -14411,13 +14420,16 @@
         <v>872</v>
       </c>
       <c r="B446" t="s">
-        <v>1649</v>
+        <v>1088</v>
+      </c>
+      <c r="C446" t="s">
+        <v>1089</v>
       </c>
       <c r="D446" t="s">
-        <v>1650</v>
+        <v>1090</v>
       </c>
       <c r="E446" t="s">
-        <v>1651</v>
+        <v>1365</v>
       </c>
       <c r="F446" t="s">
         <v>947</v>
@@ -14431,13 +14443,13 @@
         <v>872</v>
       </c>
       <c r="B447" t="s">
-        <v>741</v>
+        <v>1646</v>
       </c>
       <c r="D447" t="s">
-        <v>742</v>
+        <v>1647</v>
       </c>
       <c r="E447" t="s">
-        <v>743</v>
+        <v>1648</v>
       </c>
       <c r="F447" t="s">
         <v>871</v>
@@ -14451,19 +14463,16 @@
         <v>872</v>
       </c>
       <c r="B448" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C448" t="s">
-        <v>1367</v>
+        <v>1649</v>
       </c>
       <c r="D448" t="s">
-        <v>1368</v>
+        <v>1650</v>
       </c>
       <c r="E448" t="s">
-        <v>1369</v>
+        <v>1651</v>
       </c>
       <c r="F448" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G448" t="s">
         <v>873</v>
@@ -14474,13 +14483,13 @@
         <v>872</v>
       </c>
       <c r="B449" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D449" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E449" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F449" t="s">
         <v>871</v>
@@ -14494,13 +14503,16 @@
         <v>872</v>
       </c>
       <c r="B450" t="s">
-        <v>747</v>
+        <v>1366</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1367</v>
       </c>
       <c r="D450" t="s">
-        <v>748</v>
+        <v>1368</v>
       </c>
       <c r="E450" t="s">
-        <v>749</v>
+        <v>1369</v>
       </c>
       <c r="F450" t="s">
         <v>871</v>
@@ -14514,13 +14526,13 @@
         <v>872</v>
       </c>
       <c r="B451" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D451" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E451" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="F451" t="s">
         <v>871</v>
@@ -14534,13 +14546,13 @@
         <v>872</v>
       </c>
       <c r="B452" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="D452" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="E452" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="F452" t="s">
         <v>871</v>
@@ -14554,13 +14566,13 @@
         <v>872</v>
       </c>
       <c r="B453" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="D453" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="E453" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="F453" t="s">
         <v>871</v>
@@ -14574,16 +14586,16 @@
         <v>872</v>
       </c>
       <c r="B454" t="s">
-        <v>1091</v>
+        <v>753</v>
       </c>
       <c r="D454" t="s">
-        <v>1092</v>
+        <v>754</v>
       </c>
       <c r="E454" t="s">
-        <v>1370</v>
+        <v>755</v>
       </c>
       <c r="F454" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G454" t="s">
         <v>873</v>
@@ -14594,16 +14606,16 @@
         <v>872</v>
       </c>
       <c r="B455" t="s">
-        <v>1371</v>
+        <v>758</v>
       </c>
       <c r="D455" t="s">
-        <v>1372</v>
+        <v>759</v>
       </c>
       <c r="E455" t="s">
-        <v>1373</v>
+        <v>760</v>
       </c>
       <c r="F455" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G455" t="s">
         <v>873</v>
@@ -14614,19 +14626,19 @@
         <v>872</v>
       </c>
       <c r="B456" t="s">
-        <v>1563</v>
+        <v>1091</v>
       </c>
       <c r="D456" t="s">
-        <v>1652</v>
+        <v>1092</v>
       </c>
       <c r="E456" t="s">
-        <v>1564</v>
+        <v>1370</v>
       </c>
       <c r="F456" t="s">
         <v>947</v>
       </c>
       <c r="G456" t="s">
-        <v>1565</v>
+        <v>873</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
@@ -14634,16 +14646,16 @@
         <v>872</v>
       </c>
       <c r="B457" t="s">
-        <v>761</v>
+        <v>1371</v>
       </c>
       <c r="D457" t="s">
-        <v>762</v>
+        <v>1372</v>
       </c>
       <c r="E457" t="s">
-        <v>763</v>
+        <v>1373</v>
       </c>
       <c r="F457" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G457" t="s">
         <v>873</v>
@@ -14654,19 +14666,19 @@
         <v>872</v>
       </c>
       <c r="B458" t="s">
-        <v>1093</v>
+        <v>1563</v>
       </c>
       <c r="D458" t="s">
-        <v>1094</v>
+        <v>1652</v>
       </c>
       <c r="E458" t="s">
-        <v>1374</v>
+        <v>1564</v>
       </c>
       <c r="F458" t="s">
         <v>947</v>
       </c>
       <c r="G458" t="s">
-        <v>873</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
@@ -14674,13 +14686,13 @@
         <v>872</v>
       </c>
       <c r="B459" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D459" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E459" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="F459" t="s">
         <v>871</v>
@@ -14694,16 +14706,16 @@
         <v>872</v>
       </c>
       <c r="B460" t="s">
-        <v>767</v>
+        <v>1093</v>
       </c>
       <c r="D460" t="s">
-        <v>768</v>
+        <v>1094</v>
       </c>
       <c r="E460" t="s">
-        <v>769</v>
+        <v>1374</v>
       </c>
       <c r="F460" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G460" t="s">
         <v>873</v>
@@ -14714,13 +14726,13 @@
         <v>872</v>
       </c>
       <c r="B461" t="s">
-        <v>1653</v>
+        <v>764</v>
       </c>
       <c r="D461" t="s">
-        <v>1654</v>
+        <v>765</v>
       </c>
       <c r="E461" t="s">
-        <v>1655</v>
+        <v>766</v>
       </c>
       <c r="F461" t="s">
         <v>871</v>
@@ -14734,16 +14746,16 @@
         <v>872</v>
       </c>
       <c r="B462" t="s">
-        <v>1375</v>
+        <v>767</v>
       </c>
       <c r="D462" t="s">
-        <v>1376</v>
+        <v>768</v>
       </c>
       <c r="E462" t="s">
-        <v>1377</v>
+        <v>769</v>
       </c>
       <c r="F462" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G462" t="s">
         <v>873</v>
@@ -14754,13 +14766,13 @@
         <v>872</v>
       </c>
       <c r="B463" t="s">
-        <v>1378</v>
+        <v>1653</v>
       </c>
       <c r="D463" t="s">
-        <v>1379</v>
+        <v>1654</v>
       </c>
       <c r="E463" t="s">
-        <v>1380</v>
+        <v>1655</v>
       </c>
       <c r="F463" t="s">
         <v>871</v>
@@ -14774,13 +14786,13 @@
         <v>872</v>
       </c>
       <c r="B464" t="s">
-        <v>1523</v>
+        <v>1375</v>
       </c>
       <c r="D464" t="s">
-        <v>1524</v>
+        <v>1376</v>
       </c>
       <c r="E464" t="s">
-        <v>1525</v>
+        <v>1377</v>
       </c>
       <c r="F464" t="s">
         <v>947</v>
@@ -14794,13 +14806,13 @@
         <v>872</v>
       </c>
       <c r="B465" t="s">
-        <v>770</v>
+        <v>1378</v>
       </c>
       <c r="D465" t="s">
-        <v>771</v>
+        <v>1379</v>
       </c>
       <c r="E465" t="s">
-        <v>772</v>
+        <v>1380</v>
       </c>
       <c r="F465" t="s">
         <v>871</v>
@@ -14814,13 +14826,13 @@
         <v>872</v>
       </c>
       <c r="B466" t="s">
-        <v>1108</v>
+        <v>1523</v>
       </c>
       <c r="D466" t="s">
-        <v>1109</v>
+        <v>1524</v>
       </c>
       <c r="E466" t="s">
-        <v>1381</v>
+        <v>1525</v>
       </c>
       <c r="F466" t="s">
         <v>947</v>
@@ -14834,19 +14846,16 @@
         <v>872</v>
       </c>
       <c r="B467" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1096</v>
+        <v>770</v>
       </c>
       <c r="D467" t="s">
-        <v>1097</v>
+        <v>771</v>
       </c>
       <c r="E467" t="s">
-        <v>1382</v>
+        <v>772</v>
       </c>
       <c r="F467" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G467" t="s">
         <v>873</v>
@@ -14857,16 +14866,16 @@
         <v>872</v>
       </c>
       <c r="B468" t="s">
-        <v>773</v>
+        <v>1108</v>
       </c>
       <c r="D468" t="s">
-        <v>774</v>
+        <v>1109</v>
       </c>
       <c r="E468" t="s">
-        <v>775</v>
+        <v>1381</v>
       </c>
       <c r="F468" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G468" t="s">
         <v>873</v>
@@ -14877,16 +14886,19 @@
         <v>872</v>
       </c>
       <c r="B469" t="s">
-        <v>776</v>
+        <v>1095</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1096</v>
       </c>
       <c r="D469" t="s">
-        <v>777</v>
+        <v>1097</v>
       </c>
       <c r="E469" t="s">
-        <v>778</v>
+        <v>1382</v>
       </c>
       <c r="F469" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G469" t="s">
         <v>873</v>
@@ -14897,13 +14909,13 @@
         <v>872</v>
       </c>
       <c r="B470" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="D470" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="E470" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="F470" t="s">
         <v>871</v>
@@ -14917,16 +14929,13 @@
         <v>872</v>
       </c>
       <c r="B471" t="s">
-        <v>845</v>
-      </c>
-      <c r="C471" t="s">
-        <v>846</v>
+        <v>776</v>
       </c>
       <c r="D471" t="s">
-        <v>847</v>
+        <v>777</v>
       </c>
       <c r="E471" t="s">
-        <v>848</v>
+        <v>778</v>
       </c>
       <c r="F471" t="s">
         <v>871</v>
@@ -14940,13 +14949,13 @@
         <v>872</v>
       </c>
       <c r="B472" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D472" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E472" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="F472" t="s">
         <v>871</v>
@@ -14960,13 +14969,16 @@
         <v>872</v>
       </c>
       <c r="B473" t="s">
-        <v>785</v>
+        <v>845</v>
+      </c>
+      <c r="C473" t="s">
+        <v>846</v>
       </c>
       <c r="D473" t="s">
-        <v>786</v>
+        <v>847</v>
       </c>
       <c r="E473" t="s">
-        <v>787</v>
+        <v>848</v>
       </c>
       <c r="F473" t="s">
         <v>871</v>
@@ -14980,13 +14992,13 @@
         <v>872</v>
       </c>
       <c r="B474" t="s">
-        <v>933</v>
+        <v>782</v>
       </c>
       <c r="D474" t="s">
-        <v>1124</v>
+        <v>783</v>
       </c>
       <c r="E474" t="s">
-        <v>1181</v>
+        <v>784</v>
       </c>
       <c r="F474" t="s">
         <v>871</v>
@@ -15000,13 +15012,13 @@
         <v>872</v>
       </c>
       <c r="B475" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D475" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E475" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="F475" t="s">
         <v>871</v>
@@ -15020,13 +15032,13 @@
         <v>872</v>
       </c>
       <c r="B476" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D476" t="s">
-        <v>1383</v>
+        <v>1124</v>
       </c>
       <c r="E476" t="s">
-        <v>1384</v>
+        <v>1181</v>
       </c>
       <c r="F476" t="s">
         <v>871</v>
@@ -15040,16 +15052,16 @@
         <v>872</v>
       </c>
       <c r="B477" t="s">
-        <v>1174</v>
+        <v>788</v>
       </c>
       <c r="D477" t="s">
-        <v>1136</v>
+        <v>789</v>
       </c>
       <c r="E477" t="s">
-        <v>1175</v>
+        <v>790</v>
       </c>
       <c r="F477" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G477" t="s">
         <v>873</v>
@@ -15060,16 +15072,16 @@
         <v>872</v>
       </c>
       <c r="B478" t="s">
-        <v>1385</v>
+        <v>937</v>
       </c>
       <c r="D478" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="E478" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="F478" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G478" t="s">
         <v>873</v>
@@ -15080,13 +15092,13 @@
         <v>872</v>
       </c>
       <c r="B479" t="s">
-        <v>1098</v>
+        <v>1174</v>
       </c>
       <c r="D479" t="s">
-        <v>1099</v>
+        <v>1136</v>
       </c>
       <c r="E479" t="s">
-        <v>1388</v>
+        <v>1175</v>
       </c>
       <c r="F479" t="s">
         <v>947</v>
@@ -15100,16 +15112,16 @@
         <v>872</v>
       </c>
       <c r="B480" t="s">
-        <v>791</v>
+        <v>1385</v>
       </c>
       <c r="D480" t="s">
-        <v>792</v>
+        <v>1386</v>
       </c>
       <c r="E480" t="s">
-        <v>793</v>
+        <v>1387</v>
       </c>
       <c r="F480" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G480" t="s">
         <v>873</v>
@@ -15120,16 +15132,16 @@
         <v>872</v>
       </c>
       <c r="B481" t="s">
-        <v>794</v>
+        <v>1098</v>
       </c>
       <c r="D481" t="s">
-        <v>1389</v>
+        <v>1099</v>
       </c>
       <c r="E481" t="s">
-        <v>795</v>
+        <v>1388</v>
       </c>
       <c r="F481" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G481" t="s">
         <v>873</v>
@@ -15140,13 +15152,13 @@
         <v>872</v>
       </c>
       <c r="B482" t="s">
-        <v>1390</v>
+        <v>791</v>
       </c>
       <c r="D482" t="s">
-        <v>921</v>
+        <v>792</v>
       </c>
       <c r="E482" t="s">
-        <v>1391</v>
+        <v>793</v>
       </c>
       <c r="F482" t="s">
         <v>871</v>
@@ -15160,13 +15172,13 @@
         <v>872</v>
       </c>
       <c r="B483" t="s">
-        <v>107</v>
+        <v>794</v>
       </c>
       <c r="D483" t="s">
-        <v>1526</v>
+        <v>1389</v>
       </c>
       <c r="E483" t="s">
-        <v>108</v>
+        <v>795</v>
       </c>
       <c r="F483" t="s">
         <v>871</v>
@@ -15180,13 +15192,13 @@
         <v>872</v>
       </c>
       <c r="B484" t="s">
-        <v>112</v>
+        <v>1390</v>
       </c>
       <c r="D484" t="s">
-        <v>1527</v>
+        <v>921</v>
       </c>
       <c r="E484" t="s">
-        <v>113</v>
+        <v>1391</v>
       </c>
       <c r="F484" t="s">
         <v>871</v>
@@ -15200,13 +15212,13 @@
         <v>872</v>
       </c>
       <c r="B485" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D485" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="E485" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F485" t="s">
         <v>871</v>
@@ -15220,13 +15232,13 @@
         <v>872</v>
       </c>
       <c r="B486" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="D486" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E486" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="F486" t="s">
         <v>871</v>
@@ -15240,13 +15252,13 @@
         <v>872</v>
       </c>
       <c r="B487" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="D487" t="s">
-        <v>1392</v>
+        <v>1528</v>
       </c>
       <c r="E487" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="F487" t="s">
         <v>871</v>
@@ -15260,13 +15272,13 @@
         <v>872</v>
       </c>
       <c r="B488" t="s">
-        <v>1393</v>
+        <v>140</v>
       </c>
       <c r="D488" t="s">
-        <v>922</v>
+        <v>1529</v>
       </c>
       <c r="E488" t="s">
-        <v>1394</v>
+        <v>141</v>
       </c>
       <c r="F488" t="s">
         <v>871</v>
@@ -15280,13 +15292,13 @@
         <v>872</v>
       </c>
       <c r="B489" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="D489" t="s">
-        <v>1530</v>
+        <v>1392</v>
       </c>
       <c r="E489" t="s">
-        <v>1216</v>
+        <v>146</v>
       </c>
       <c r="F489" t="s">
         <v>871</v>
@@ -15300,13 +15312,13 @@
         <v>872</v>
       </c>
       <c r="B490" t="s">
-        <v>185</v>
+        <v>1393</v>
       </c>
       <c r="D490" t="s">
-        <v>1531</v>
+        <v>922</v>
       </c>
       <c r="E490" t="s">
-        <v>186</v>
+        <v>1394</v>
       </c>
       <c r="F490" t="s">
         <v>871</v>
@@ -15320,13 +15332,13 @@
         <v>872</v>
       </c>
       <c r="B491" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D491" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="E491" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F491" t="s">
         <v>871</v>
@@ -15340,13 +15352,13 @@
         <v>872</v>
       </c>
       <c r="B492" t="s">
-        <v>273</v>
+        <v>185</v>
       </c>
       <c r="D492" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="E492" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="F492" t="s">
         <v>871</v>
@@ -15360,16 +15372,16 @@
         <v>872</v>
       </c>
       <c r="B493" t="s">
-        <v>1015</v>
+        <v>196</v>
       </c>
       <c r="D493" t="s">
-        <v>1114</v>
+        <v>1532</v>
       </c>
       <c r="E493" t="s">
-        <v>1176</v>
+        <v>1217</v>
       </c>
       <c r="F493" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G493" t="s">
         <v>873</v>
@@ -15380,16 +15392,13 @@
         <v>872</v>
       </c>
       <c r="B494" t="s">
-        <v>884</v>
-      </c>
-      <c r="C494" t="s">
-        <v>885</v>
+        <v>273</v>
       </c>
       <c r="D494" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="E494" t="s">
-        <v>886</v>
+        <v>274</v>
       </c>
       <c r="F494" t="s">
         <v>871</v>
@@ -15403,13 +15412,13 @@
         <v>872</v>
       </c>
       <c r="B495" t="s">
-        <v>418</v>
+        <v>1015</v>
       </c>
       <c r="D495" t="s">
-        <v>1535</v>
+        <v>1114</v>
       </c>
       <c r="E495" t="s">
-        <v>419</v>
+        <v>1176</v>
       </c>
       <c r="F495" t="s">
         <v>947</v>
@@ -15423,13 +15432,16 @@
         <v>872</v>
       </c>
       <c r="B496" t="s">
-        <v>420</v>
+        <v>884</v>
+      </c>
+      <c r="C496" t="s">
+        <v>885</v>
       </c>
       <c r="D496" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="E496" t="s">
-        <v>421</v>
+        <v>886</v>
       </c>
       <c r="F496" t="s">
         <v>871</v>
@@ -15443,16 +15455,16 @@
         <v>872</v>
       </c>
       <c r="B497" t="s">
-        <v>1395</v>
+        <v>418</v>
       </c>
       <c r="D497" t="s">
-        <v>1588</v>
+        <v>1535</v>
       </c>
       <c r="E497" t="s">
-        <v>1396</v>
+        <v>419</v>
       </c>
       <c r="F497" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G497" t="s">
         <v>873</v>
@@ -15463,13 +15475,13 @@
         <v>872</v>
       </c>
       <c r="B498" t="s">
-        <v>1183</v>
+        <v>420</v>
       </c>
       <c r="D498" t="s">
-        <v>923</v>
+        <v>1536</v>
       </c>
       <c r="E498" t="s">
-        <v>1182</v>
+        <v>421</v>
       </c>
       <c r="F498" t="s">
         <v>871</v>
@@ -15483,13 +15495,13 @@
         <v>872</v>
       </c>
       <c r="B499" t="s">
-        <v>503</v>
+        <v>1395</v>
       </c>
       <c r="D499" t="s">
-        <v>1537</v>
+        <v>1588</v>
       </c>
       <c r="E499" t="s">
-        <v>504</v>
+        <v>1396</v>
       </c>
       <c r="F499" t="s">
         <v>871</v>
@@ -15503,13 +15515,13 @@
         <v>872</v>
       </c>
       <c r="B500" t="s">
-        <v>1397</v>
+        <v>1183</v>
       </c>
       <c r="D500" t="s">
-        <v>1398</v>
+        <v>923</v>
       </c>
       <c r="E500" t="s">
-        <v>1399</v>
+        <v>1182</v>
       </c>
       <c r="F500" t="s">
         <v>871</v>
@@ -15523,13 +15535,13 @@
         <v>872</v>
       </c>
       <c r="B501" t="s">
-        <v>632</v>
+        <v>503</v>
       </c>
       <c r="D501" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E501" t="s">
-        <v>633</v>
+        <v>504</v>
       </c>
       <c r="F501" t="s">
         <v>871</v>
@@ -15543,13 +15555,13 @@
         <v>872</v>
       </c>
       <c r="B502" t="s">
-        <v>642</v>
+        <v>1397</v>
       </c>
       <c r="D502" t="s">
-        <v>1539</v>
+        <v>1398</v>
       </c>
       <c r="E502" t="s">
-        <v>643</v>
+        <v>1399</v>
       </c>
       <c r="F502" t="s">
         <v>871</v>
@@ -15563,16 +15575,16 @@
         <v>872</v>
       </c>
       <c r="B503" t="s">
-        <v>1177</v>
+        <v>632</v>
       </c>
       <c r="D503" t="s">
-        <v>1137</v>
+        <v>1538</v>
       </c>
       <c r="E503" t="s">
-        <v>1178</v>
+        <v>633</v>
       </c>
       <c r="F503" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G503" t="s">
         <v>873</v>
@@ -15583,13 +15595,13 @@
         <v>872</v>
       </c>
       <c r="B504" t="s">
-        <v>664</v>
+        <v>642</v>
       </c>
       <c r="D504" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="E504" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="F504" t="s">
         <v>871</v>
@@ -15603,16 +15615,16 @@
         <v>872</v>
       </c>
       <c r="B505" t="s">
-        <v>696</v>
+        <v>1177</v>
       </c>
       <c r="D505" t="s">
-        <v>1541</v>
+        <v>1137</v>
       </c>
       <c r="E505" t="s">
-        <v>697</v>
+        <v>1178</v>
       </c>
       <c r="F505" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G505" t="s">
         <v>873</v>
@@ -15623,16 +15635,13 @@
         <v>872</v>
       </c>
       <c r="B506" t="s">
-        <v>890</v>
-      </c>
-      <c r="C506" t="s">
-        <v>891</v>
+        <v>664</v>
       </c>
       <c r="D506" t="s">
-        <v>892</v>
+        <v>1540</v>
       </c>
       <c r="E506" t="s">
-        <v>893</v>
+        <v>665</v>
       </c>
       <c r="F506" t="s">
         <v>871</v>
@@ -15646,13 +15655,13 @@
         <v>872</v>
       </c>
       <c r="B507" t="s">
-        <v>730</v>
+        <v>696</v>
       </c>
       <c r="D507" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E507" t="s">
-        <v>731</v>
+        <v>697</v>
       </c>
       <c r="F507" t="s">
         <v>871</v>
@@ -15666,16 +15675,16 @@
         <v>872</v>
       </c>
       <c r="B508" t="s">
-        <v>833</v>
+        <v>890</v>
       </c>
       <c r="C508" t="s">
-        <v>834</v>
+        <v>891</v>
       </c>
       <c r="D508" t="s">
-        <v>835</v>
+        <v>892</v>
       </c>
       <c r="E508" t="s">
-        <v>836</v>
+        <v>893</v>
       </c>
       <c r="F508" t="s">
         <v>871</v>
@@ -15689,13 +15698,13 @@
         <v>872</v>
       </c>
       <c r="B509" t="s">
-        <v>756</v>
+        <v>730</v>
       </c>
       <c r="D509" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="E509" t="s">
-        <v>757</v>
+        <v>731</v>
       </c>
       <c r="F509" t="s">
         <v>871</v>
@@ -15709,13 +15718,16 @@
         <v>872</v>
       </c>
       <c r="B510" t="s">
-        <v>1589</v>
+        <v>833</v>
+      </c>
+      <c r="C510" t="s">
+        <v>834</v>
       </c>
       <c r="D510" t="s">
-        <v>1590</v>
+        <v>835</v>
       </c>
       <c r="E510" t="s">
-        <v>1591</v>
+        <v>836</v>
       </c>
       <c r="F510" t="s">
         <v>871</v>
@@ -15729,13 +15741,13 @@
         <v>872</v>
       </c>
       <c r="B511" t="s">
-        <v>821</v>
+        <v>756</v>
       </c>
       <c r="D511" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="E511" t="s">
-        <v>822</v>
+        <v>757</v>
       </c>
       <c r="F511" t="s">
         <v>871</v>
@@ -15749,13 +15761,13 @@
         <v>872</v>
       </c>
       <c r="B512" t="s">
-        <v>823</v>
+        <v>1589</v>
       </c>
       <c r="D512" t="s">
-        <v>1545</v>
+        <v>1590</v>
       </c>
       <c r="E512" t="s">
-        <v>824</v>
+        <v>1591</v>
       </c>
       <c r="F512" t="s">
         <v>871</v>
@@ -15769,13 +15781,13 @@
         <v>872</v>
       </c>
       <c r="B513" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="D513" t="s">
-        <v>797</v>
+        <v>1544</v>
       </c>
       <c r="E513" t="s">
-        <v>798</v>
+        <v>822</v>
       </c>
       <c r="F513" t="s">
         <v>871</v>
@@ -15789,13 +15801,13 @@
         <v>872</v>
       </c>
       <c r="B514" t="s">
-        <v>799</v>
+        <v>823</v>
       </c>
       <c r="D514" t="s">
-        <v>800</v>
+        <v>1545</v>
       </c>
       <c r="E514" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="F514" t="s">
         <v>871</v>
@@ -15809,16 +15821,16 @@
         <v>872</v>
       </c>
       <c r="B515" t="s">
-        <v>1100</v>
+        <v>796</v>
       </c>
       <c r="D515" t="s">
-        <v>1101</v>
+        <v>797</v>
       </c>
       <c r="E515" t="s">
-        <v>1400</v>
+        <v>798</v>
       </c>
       <c r="F515" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G515" t="s">
         <v>873</v>
@@ -15829,16 +15841,13 @@
         <v>872</v>
       </c>
       <c r="B516" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1547</v>
+        <v>799</v>
       </c>
       <c r="D516" t="s">
-        <v>1548</v>
+        <v>800</v>
       </c>
       <c r="E516" t="s">
-        <v>1549</v>
+        <v>801</v>
       </c>
       <c r="F516" t="s">
         <v>871</v>
@@ -15852,16 +15861,16 @@
         <v>872</v>
       </c>
       <c r="B517" t="s">
-        <v>802</v>
+        <v>1100</v>
       </c>
       <c r="D517" t="s">
-        <v>803</v>
+        <v>1101</v>
       </c>
       <c r="E517" t="s">
-        <v>804</v>
+        <v>1400</v>
       </c>
       <c r="F517" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G517" t="s">
         <v>873</v>
@@ -15872,16 +15881,19 @@
         <v>872</v>
       </c>
       <c r="B518" t="s">
-        <v>1102</v>
+        <v>1546</v>
+      </c>
+      <c r="C518" t="s">
+        <v>1547</v>
       </c>
       <c r="D518" t="s">
-        <v>1103</v>
+        <v>1548</v>
       </c>
       <c r="E518" t="s">
-        <v>1401</v>
+        <v>1549</v>
       </c>
       <c r="F518" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G518" t="s">
         <v>873</v>
@@ -15892,13 +15904,13 @@
         <v>872</v>
       </c>
       <c r="B519" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D519" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E519" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="F519" t="s">
         <v>871</v>
@@ -15912,13 +15924,13 @@
         <v>872</v>
       </c>
       <c r="B520" t="s">
-        <v>1550</v>
+        <v>1102</v>
       </c>
       <c r="D520" t="s">
-        <v>1551</v>
+        <v>1103</v>
       </c>
       <c r="E520" t="s">
-        <v>1552</v>
+        <v>1401</v>
       </c>
       <c r="F520" t="s">
         <v>947</v>
@@ -15932,16 +15944,16 @@
         <v>872</v>
       </c>
       <c r="B521" t="s">
-        <v>1104</v>
+        <v>805</v>
       </c>
       <c r="D521" t="s">
-        <v>1105</v>
+        <v>806</v>
       </c>
       <c r="E521" t="s">
-        <v>1402</v>
+        <v>807</v>
       </c>
       <c r="F521" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G521" t="s">
         <v>873</v>
@@ -15952,16 +15964,16 @@
         <v>872</v>
       </c>
       <c r="B522" t="s">
-        <v>808</v>
+        <v>1550</v>
       </c>
       <c r="D522" t="s">
-        <v>809</v>
+        <v>1551</v>
       </c>
       <c r="E522" t="s">
-        <v>810</v>
+        <v>1552</v>
       </c>
       <c r="F522" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G522" t="s">
         <v>873</v>
@@ -15972,16 +15984,16 @@
         <v>872</v>
       </c>
       <c r="B523" t="s">
-        <v>811</v>
+        <v>1104</v>
       </c>
       <c r="D523" t="s">
-        <v>812</v>
+        <v>1105</v>
       </c>
       <c r="E523" t="s">
-        <v>813</v>
+        <v>1402</v>
       </c>
       <c r="F523" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G523" t="s">
         <v>873</v>
@@ -15992,13 +16004,13 @@
         <v>872</v>
       </c>
       <c r="B524" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D524" t="s">
-        <v>1403</v>
+        <v>809</v>
       </c>
       <c r="E524" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="F524" t="s">
         <v>871</v>
@@ -16012,16 +16024,16 @@
         <v>872</v>
       </c>
       <c r="B525" t="s">
-        <v>1106</v>
+        <v>811</v>
       </c>
       <c r="D525" t="s">
-        <v>1107</v>
+        <v>812</v>
       </c>
       <c r="E525" t="s">
-        <v>1404</v>
+        <v>813</v>
       </c>
       <c r="F525" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="G525" t="s">
         <v>873</v>
@@ -16032,13 +16044,13 @@
         <v>872</v>
       </c>
       <c r="B526" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D526" t="s">
-        <v>819</v>
+        <v>1403</v>
       </c>
       <c r="E526" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="F526" t="s">
         <v>871</v>
@@ -16052,16 +16064,16 @@
         <v>872</v>
       </c>
       <c r="B527" t="s">
-        <v>825</v>
+        <v>1106</v>
       </c>
       <c r="D527" t="s">
-        <v>826</v>
+        <v>1107</v>
       </c>
       <c r="E527" t="s">
-        <v>827</v>
+        <v>1404</v>
       </c>
       <c r="F527" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="G527" t="s">
         <v>873</v>
@@ -16072,13 +16084,13 @@
         <v>872</v>
       </c>
       <c r="B528" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
       <c r="D528" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="E528" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="F528" t="s">
         <v>871</v>
@@ -16092,13 +16104,13 @@
         <v>872</v>
       </c>
       <c r="B529" t="s">
-        <v>1566</v>
+        <v>825</v>
       </c>
       <c r="D529" t="s">
-        <v>1567</v>
+        <v>826</v>
       </c>
       <c r="E529" t="s">
-        <v>1568</v>
+        <v>827</v>
       </c>
       <c r="F529" t="s">
         <v>871</v>
@@ -16112,13 +16124,13 @@
         <v>872</v>
       </c>
       <c r="B530" t="s">
-        <v>1569</v>
+        <v>828</v>
       </c>
       <c r="D530" t="s">
-        <v>1570</v>
+        <v>829</v>
       </c>
       <c r="E530" t="s">
-        <v>1571</v>
+        <v>830</v>
       </c>
       <c r="F530" t="s">
         <v>871</v>
@@ -16132,13 +16144,13 @@
         <v>872</v>
       </c>
       <c r="B531" t="s">
-        <v>1405</v>
+        <v>1566</v>
       </c>
       <c r="D531" t="s">
-        <v>831</v>
+        <v>1567</v>
       </c>
       <c r="E531" t="s">
-        <v>832</v>
+        <v>1568</v>
       </c>
       <c r="F531" t="s">
         <v>871</v>
@@ -16152,18 +16164,38 @@
         <v>872</v>
       </c>
       <c r="B532" t="s">
-        <v>1656</v>
+        <v>1569</v>
       </c>
       <c r="D532" t="s">
-        <v>1657</v>
+        <v>1570</v>
       </c>
       <c r="E532" t="s">
-        <v>1658</v>
+        <v>1571</v>
       </c>
       <c r="F532" t="s">
         <v>871</v>
       </c>
       <c r="G532" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>872</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D533" t="s">
+        <v>831</v>
+      </c>
+      <c r="E533" t="s">
+        <v>832</v>
+      </c>
+      <c r="F533" t="s">
+        <v>871</v>
+      </c>
+      <c r="G533" t="s">
         <v>873</v>
       </c>
     </row>
